--- a/diseases/d085/2020-2025.xlsx
+++ b/diseases/d085/2020-2025.xlsx
@@ -50433,12 +50433,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -50472,13 +50472,13 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="O275" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="R275" t="n">
-        <v>0</v>
+        <v>0.1728062199660442</v>
       </c>
       <c r="S275" t="inlineStr">
         <is>
@@ -50487,7 +50487,7 @@
       </c>
       <c r="U275" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -50512,7 +50512,7 @@
       </c>
       <c r="AS275" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT275" t="n">
@@ -50530,7 +50530,7 @@
       </c>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
@@ -50550,7 +50550,7 @@
       </c>
       <c r="BA275" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB275" t="inlineStr">
@@ -50592,12 +50592,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -50631,24 +50631,24 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="O276" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="U276" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V276" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W276" t="inlineStr">
         <is>
-          <t>SRC_HR_ECDC_ATLAS</t>
+          <t>SRC_FR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X276" t="inlineStr">
@@ -50678,7 +50678,7 @@
       </c>
       <c r="AC276" t="inlineStr">
         <is>
-          <t>country:HR:national</t>
+          <t>country:FR:national</t>
         </is>
       </c>
       <c r="AD276" t="inlineStr">
@@ -50718,7 +50718,7 @@
       </c>
       <c r="AK276" t="inlineStr">
         <is>
-          <t>Croatia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM276" t="inlineStr">
@@ -50746,7 +50746,7 @@
       </c>
       <c r="AS276" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT276" t="n">
@@ -50764,7 +50764,7 @@
       </c>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
@@ -50784,7 +50784,7 @@
       </c>
       <c r="BA276" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB276" t="inlineStr">
@@ -50826,12 +50826,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -50865,13 +50865,13 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O277" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R277" t="n">
-        <v>0.02066941090990415</v>
+        <v>0</v>
       </c>
       <c r="S277" t="inlineStr">
         <is>
@@ -50880,7 +50880,7 @@
       </c>
       <c r="U277" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -50905,7 +50905,7 @@
       </c>
       <c r="AS277" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT277" t="n">
@@ -50923,7 +50923,7 @@
       </c>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
@@ -50943,7 +50943,7 @@
       </c>
       <c r="BA277" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="BB277" t="inlineStr">
@@ -50985,12 +50985,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -51024,24 +51024,24 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O278" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U278" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V278" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W278" t="inlineStr">
         <is>
-          <t>SRC_HU_ECDC_ATLAS</t>
+          <t>SRC_HR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X278" t="inlineStr">
@@ -51071,7 +51071,7 @@
       </c>
       <c r="AC278" t="inlineStr">
         <is>
-          <t>country:HU:national</t>
+          <t>country:HR:national</t>
         </is>
       </c>
       <c r="AD278" t="inlineStr">
@@ -51111,7 +51111,7 @@
       </c>
       <c r="AK278" t="inlineStr">
         <is>
-          <t>Hungary annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Croatia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM278" t="inlineStr">
@@ -51139,7 +51139,7 @@
       </c>
       <c r="AS278" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT278" t="n">
@@ -51157,7 +51157,7 @@
       </c>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
@@ -51177,7 +51177,7 @@
       </c>
       <c r="BA278" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="BB278" t="inlineStr">
@@ -51219,12 +51219,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -51258,13 +51258,13 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O279" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R279" t="n">
-        <v>0</v>
+        <v>0.02066941090990415</v>
       </c>
       <c r="S279" t="inlineStr">
         <is>
@@ -51273,7 +51273,7 @@
       </c>
       <c r="U279" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -51298,7 +51298,7 @@
       </c>
       <c r="AS279" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT279" t="n">
@@ -51311,42 +51311,42 @@
       </c>
       <c r="AV279" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA279" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB279" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC279" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -51378,12 +51378,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -51417,24 +51417,24 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O280" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U280" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V280" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W280" t="inlineStr">
         <is>
-          <t>SRC_IE_ECDC_ATLAS</t>
+          <t>SRC_HU_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X280" t="inlineStr">
@@ -51464,7 +51464,7 @@
       </c>
       <c r="AC280" t="inlineStr">
         <is>
-          <t>country:IE:national</t>
+          <t>country:HU:national</t>
         </is>
       </c>
       <c r="AD280" t="inlineStr">
@@ -51504,7 +51504,7 @@
       </c>
       <c r="AK280" t="inlineStr">
         <is>
-          <t>Ireland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Hungary annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM280" t="inlineStr">
@@ -51532,7 +51532,7 @@
       </c>
       <c r="AS280" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT280" t="n">
@@ -51545,42 +51545,42 @@
       </c>
       <c r="AV280" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA280" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB280" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC280" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -51607,17 +51607,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -51656,34 +51656,17 @@
       <c r="O281" t="n">
         <v>0</v>
       </c>
+      <c r="R281" t="n">
+        <v>0</v>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U281" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V281" t="inlineStr">
-        <is>
-          <t>SER_IS_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W281" t="inlineStr">
-        <is>
-          <t>SRC_IS_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X281" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis, congenital</t>
-        </is>
-      </c>
-      <c r="Y281" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z281" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
@@ -51691,64 +51674,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB281" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC281" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD281" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE281" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF281" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG281" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH281" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI281" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ281" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK281" t="inlineStr">
-        <is>
-          <t>Iceland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM281" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN281" t="b">
-        <v>0</v>
-      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -51756,7 +51681,7 @@
       </c>
       <c r="AP281" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ281" t="inlineStr">
@@ -51764,62 +51689,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR281" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS281" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT281" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV281" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
       <c r="AZ281" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="BA281" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="BB281" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="BC281" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
     </row>
@@ -51846,17 +51766,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -51890,29 +51810,104 @@
         </is>
       </c>
       <c r="N282" t="n">
+        <v>0</v>
+      </c>
+      <c r="O282" t="n">
+        <v>0</v>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>SRC_IE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB282" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC282" t="inlineStr">
+        <is>
+          <t>country:IE:national</t>
+        </is>
+      </c>
+      <c r="AD282" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE282" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF282" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG282" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH282" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI282" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ282" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK282" t="inlineStr">
+        <is>
+          <t>Ireland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM282" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN282" t="b">
         <v>1</v>
       </c>
-      <c r="O282" t="n">
-        <v>1</v>
-      </c>
-      <c r="R282" t="n">
-        <v>0.001685122493323418</v>
-      </c>
-      <c r="S282" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U282" t="inlineStr">
-        <is>
-          <t>SER_IT_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA282" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -51930,7 +51925,7 @@
       </c>
       <c r="AS282" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT282" t="n">
@@ -51943,42 +51938,42 @@
       </c>
       <c r="AV282" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
       <c r="AZ282" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="BA282" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="BB282" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="BC282" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
     </row>
@@ -52010,12 +52005,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -52049,24 +52044,24 @@
         </is>
       </c>
       <c r="N283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U283" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_IS_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V283" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_IS_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W283" t="inlineStr">
         <is>
-          <t>SRC_IT_ECDC_ATLAS</t>
+          <t>SRC_IS_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X283" t="inlineStr">
@@ -52096,7 +52091,7 @@
       </c>
       <c r="AC283" t="inlineStr">
         <is>
-          <t>country:IT:national</t>
+          <t>country:IS:national</t>
         </is>
       </c>
       <c r="AD283" t="inlineStr">
@@ -52136,7 +52131,7 @@
       </c>
       <c r="AK283" t="inlineStr">
         <is>
-          <t>Italy annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Iceland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM283" t="inlineStr">
@@ -52145,7 +52140,7 @@
         </is>
       </c>
       <c r="AN283" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO283" t="inlineStr">
         <is>
@@ -52154,7 +52149,7 @@
       </c>
       <c r="AP283" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ283" t="inlineStr">
@@ -52162,57 +52157,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR283" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS283" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT283" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV283" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ283" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA283" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB283" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC283" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -52244,12 +52244,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -52283,13 +52283,13 @@
         </is>
       </c>
       <c r="N284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R284" t="n">
-        <v>0</v>
+        <v>0.001685122493323418</v>
       </c>
       <c r="S284" t="inlineStr">
         <is>
@@ -52298,7 +52298,7 @@
       </c>
       <c r="U284" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_IT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
@@ -52323,7 +52323,7 @@
       </c>
       <c r="AS284" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_IT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT284" t="n">
@@ -52341,7 +52341,7 @@
       </c>
       <c r="AW284" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX284" t="inlineStr">
@@ -52361,7 +52361,7 @@
       </c>
       <c r="BA284" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB284" t="inlineStr">
@@ -52403,12 +52403,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -52442,24 +52442,24 @@
         </is>
       </c>
       <c r="N285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U285" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_IT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V285" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_IT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W285" t="inlineStr">
         <is>
-          <t>SRC_LT_ECDC_ATLAS</t>
+          <t>SRC_IT_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X285" t="inlineStr">
@@ -52489,7 +52489,7 @@
       </c>
       <c r="AC285" t="inlineStr">
         <is>
-          <t>country:LT:national</t>
+          <t>country:IT:national</t>
         </is>
       </c>
       <c r="AD285" t="inlineStr">
@@ -52529,7 +52529,7 @@
       </c>
       <c r="AK285" t="inlineStr">
         <is>
-          <t>Lithuania annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Italy annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM285" t="inlineStr">
@@ -52557,7 +52557,7 @@
       </c>
       <c r="AS285" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_IT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT285" t="n">
@@ -52575,7 +52575,7 @@
       </c>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
@@ -52595,7 +52595,7 @@
       </c>
       <c r="BA285" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB285" t="inlineStr">
@@ -52637,12 +52637,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -52691,7 +52691,7 @@
       </c>
       <c r="U286" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -52716,7 +52716,7 @@
       </c>
       <c r="AS286" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT286" t="n">
@@ -52734,7 +52734,7 @@
       </c>
       <c r="AW286" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="AX286" t="inlineStr">
@@ -52754,7 +52754,7 @@
       </c>
       <c r="BA286" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="BB286" t="inlineStr">
@@ -52796,12 +52796,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -52842,17 +52842,17 @@
       </c>
       <c r="U287" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V287" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W287" t="inlineStr">
         <is>
-          <t>SRC_LU_ECDC_ATLAS</t>
+          <t>SRC_LT_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X287" t="inlineStr">
@@ -52882,7 +52882,7 @@
       </c>
       <c r="AC287" t="inlineStr">
         <is>
-          <t>country:LU:national</t>
+          <t>country:LT:national</t>
         </is>
       </c>
       <c r="AD287" t="inlineStr">
@@ -52922,7 +52922,7 @@
       </c>
       <c r="AK287" t="inlineStr">
         <is>
-          <t>Luxembourg annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Lithuania annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM287" t="inlineStr">
@@ -52950,7 +52950,7 @@
       </c>
       <c r="AS287" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT287" t="n">
@@ -52968,7 +52968,7 @@
       </c>
       <c r="AW287" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="AX287" t="inlineStr">
@@ -52988,7 +52988,7 @@
       </c>
       <c r="BA287" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="BB287" t="inlineStr">
@@ -53030,12 +53030,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -53069,13 +53069,13 @@
         </is>
       </c>
       <c r="N288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R288" t="n">
-        <v>0.05342247050612182</v>
+        <v>0</v>
       </c>
       <c r="S288" t="inlineStr">
         <is>
@@ -53084,7 +53084,7 @@
       </c>
       <c r="U288" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -53109,7 +53109,7 @@
       </c>
       <c r="AS288" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT288" t="n">
@@ -53127,7 +53127,7 @@
       </c>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
@@ -53147,7 +53147,7 @@
       </c>
       <c r="BA288" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB288" t="inlineStr">
@@ -53189,12 +53189,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -53228,24 +53228,24 @@
         </is>
       </c>
       <c r="N289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U289" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V289" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W289" t="inlineStr">
         <is>
-          <t>SRC_LV_ECDC_ATLAS</t>
+          <t>SRC_LU_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X289" t="inlineStr">
@@ -53275,7 +53275,7 @@
       </c>
       <c r="AC289" t="inlineStr">
         <is>
-          <t>country:LV:national</t>
+          <t>country:LU:national</t>
         </is>
       </c>
       <c r="AD289" t="inlineStr">
@@ -53315,7 +53315,7 @@
       </c>
       <c r="AK289" t="inlineStr">
         <is>
-          <t>Latvia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Luxembourg annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM289" t="inlineStr">
@@ -53343,7 +53343,7 @@
       </c>
       <c r="AS289" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT289" t="n">
@@ -53361,7 +53361,7 @@
       </c>
       <c r="AW289" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX289" t="inlineStr">
@@ -53381,7 +53381,7 @@
       </c>
       <c r="BA289" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB289" t="inlineStr">
@@ -53423,12 +53423,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -53462,13 +53462,13 @@
         </is>
       </c>
       <c r="N290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R290" t="n">
-        <v>0</v>
+        <v>0.05342247050612182</v>
       </c>
       <c r="S290" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
       </c>
       <c r="U290" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
@@ -53502,7 +53502,7 @@
       </c>
       <c r="AS290" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT290" t="n">
@@ -53520,7 +53520,7 @@
       </c>
       <c r="AW290" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX290" t="inlineStr">
@@ -53540,7 +53540,7 @@
       </c>
       <c r="BA290" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB290" t="inlineStr">
@@ -53582,12 +53582,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -53621,24 +53621,24 @@
         </is>
       </c>
       <c r="N291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U291" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V291" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W291" t="inlineStr">
         <is>
-          <t>SRC_MT_ECDC_ATLAS</t>
+          <t>SRC_LV_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X291" t="inlineStr">
@@ -53668,7 +53668,7 @@
       </c>
       <c r="AC291" t="inlineStr">
         <is>
-          <t>country:MT:national</t>
+          <t>country:LV:national</t>
         </is>
       </c>
       <c r="AD291" t="inlineStr">
@@ -53708,7 +53708,7 @@
       </c>
       <c r="AK291" t="inlineStr">
         <is>
-          <t>Malta annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Latvia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM291" t="inlineStr">
@@ -53736,7 +53736,7 @@
       </c>
       <c r="AS291" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT291" t="n">
@@ -53754,7 +53754,7 @@
       </c>
       <c r="AW291" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX291" t="inlineStr">
@@ -53774,7 +53774,7 @@
       </c>
       <c r="BA291" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB291" t="inlineStr">
@@ -53816,12 +53816,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -53855,13 +53855,13 @@
         </is>
       </c>
       <c r="N292" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O292" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R292" t="n">
-        <v>0.03113712710338754</v>
+        <v>0</v>
       </c>
       <c r="S292" t="inlineStr">
         <is>
@@ -53870,7 +53870,7 @@
       </c>
       <c r="U292" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
+          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
@@ -53895,7 +53895,7 @@
       </c>
       <c r="AS292" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
+          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT292" t="n">
@@ -53913,7 +53913,7 @@
       </c>
       <c r="AW292" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX292" t="inlineStr">
@@ -53933,7 +53933,7 @@
       </c>
       <c r="BA292" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB292" t="inlineStr">
@@ -53975,12 +53975,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -54014,24 +54014,24 @@
         </is>
       </c>
       <c r="N293" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O293" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="U293" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
+          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V293" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
+          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W293" t="inlineStr">
         <is>
-          <t>SRC_PL_ECDC_ATLAS</t>
+          <t>SRC_MT_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X293" t="inlineStr">
@@ -54061,7 +54061,7 @@
       </c>
       <c r="AC293" t="inlineStr">
         <is>
-          <t>country:PL:national</t>
+          <t>country:MT:national</t>
         </is>
       </c>
       <c r="AD293" t="inlineStr">
@@ -54101,7 +54101,7 @@
       </c>
       <c r="AK293" t="inlineStr">
         <is>
-          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Malta annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM293" t="inlineStr">
@@ -54129,7 +54129,7 @@
       </c>
       <c r="AS293" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
+          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT293" t="n">
@@ -54147,7 +54147,7 @@
       </c>
       <c r="AW293" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX293" t="inlineStr">
@@ -54167,7 +54167,7 @@
       </c>
       <c r="BA293" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB293" t="inlineStr">
@@ -54209,12 +54209,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -54248,13 +54248,13 @@
         </is>
       </c>
       <c r="N294" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O294" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="R294" t="n">
-        <v>0.01918411401886326</v>
+        <v>0.03113712710338754</v>
       </c>
       <c r="S294" t="inlineStr">
         <is>
@@ -54263,7 +54263,7 @@
       </c>
       <c r="U294" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -54288,7 +54288,7 @@
       </c>
       <c r="AS294" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT294" t="n">
@@ -54306,7 +54306,7 @@
       </c>
       <c r="AW294" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX294" t="inlineStr">
@@ -54326,7 +54326,7 @@
       </c>
       <c r="BA294" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB294" t="inlineStr">
@@ -54368,12 +54368,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -54407,24 +54407,24 @@
         </is>
       </c>
       <c r="N295" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O295" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="U295" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V295" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W295" t="inlineStr">
         <is>
-          <t>SRC_PT_ECDC_ATLAS</t>
+          <t>SRC_PL_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X295" t="inlineStr">
@@ -54454,7 +54454,7 @@
       </c>
       <c r="AC295" t="inlineStr">
         <is>
-          <t>country:PT:national</t>
+          <t>country:PL:national</t>
         </is>
       </c>
       <c r="AD295" t="inlineStr">
@@ -54494,7 +54494,7 @@
       </c>
       <c r="AK295" t="inlineStr">
         <is>
-          <t>Portugal annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM295" t="inlineStr">
@@ -54522,7 +54522,7 @@
       </c>
       <c r="AS295" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT295" t="n">
@@ -54540,7 +54540,7 @@
       </c>
       <c r="AW295" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX295" t="inlineStr">
@@ -54560,7 +54560,7 @@
       </c>
       <c r="BA295" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB295" t="inlineStr">
@@ -54602,12 +54602,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -54641,13 +54641,13 @@
         </is>
       </c>
       <c r="N296" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O296" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R296" t="n">
-        <v>0.005258981709682332</v>
+        <v>0.01918411401886326</v>
       </c>
       <c r="S296" t="inlineStr">
         <is>
@@ -54656,7 +54656,7 @@
       </c>
       <c r="U296" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
@@ -54681,7 +54681,7 @@
       </c>
       <c r="AS296" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT296" t="n">
@@ -54699,7 +54699,7 @@
       </c>
       <c r="AW296" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="AX296" t="inlineStr">
@@ -54719,7 +54719,7 @@
       </c>
       <c r="BA296" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="BB296" t="inlineStr">
@@ -54761,12 +54761,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -54800,24 +54800,24 @@
         </is>
       </c>
       <c r="N297" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O297" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U297" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V297" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W297" t="inlineStr">
         <is>
-          <t>SRC_RO_ECDC_ATLAS</t>
+          <t>SRC_PT_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X297" t="inlineStr">
@@ -54847,7 +54847,7 @@
       </c>
       <c r="AC297" t="inlineStr">
         <is>
-          <t>country:RO:national</t>
+          <t>country:PT:national</t>
         </is>
       </c>
       <c r="AD297" t="inlineStr">
@@ -54887,7 +54887,7 @@
       </c>
       <c r="AK297" t="inlineStr">
         <is>
-          <t>Romania annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Portugal annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM297" t="inlineStr">
@@ -54915,7 +54915,7 @@
       </c>
       <c r="AS297" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT297" t="n">
@@ -54933,7 +54933,7 @@
       </c>
       <c r="AW297" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="AX297" t="inlineStr">
@@ -54953,7 +54953,7 @@
       </c>
       <c r="BA297" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="BB297" t="inlineStr">
@@ -54995,12 +54995,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -55034,13 +55034,13 @@
         </is>
       </c>
       <c r="N298" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O298" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R298" t="n">
-        <v>0.09439766384661513</v>
+        <v>0.005258981709682332</v>
       </c>
       <c r="S298" t="inlineStr">
         <is>
@@ -55049,7 +55049,7 @@
       </c>
       <c r="U298" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -55074,7 +55074,7 @@
       </c>
       <c r="AS298" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT298" t="n">
@@ -55092,7 +55092,7 @@
       </c>
       <c r="AW298" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="AX298" t="inlineStr">
@@ -55112,7 +55112,7 @@
       </c>
       <c r="BA298" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="BB298" t="inlineStr">
@@ -55154,12 +55154,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -55193,24 +55193,24 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O299" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U299" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W299" t="inlineStr">
         <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
+          <t>SRC_RO_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X299" t="inlineStr">
@@ -55240,7 +55240,7 @@
       </c>
       <c r="AC299" t="inlineStr">
         <is>
-          <t>country:SI:national</t>
+          <t>country:RO:national</t>
         </is>
       </c>
       <c r="AD299" t="inlineStr">
@@ -55280,7 +55280,7 @@
       </c>
       <c r="AK299" t="inlineStr">
         <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Romania annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM299" t="inlineStr">
@@ -55308,7 +55308,7 @@
       </c>
       <c r="AS299" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT299" t="n">
@@ -55326,7 +55326,7 @@
       </c>
       <c r="AW299" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="AX299" t="inlineStr">
@@ -55346,7 +55346,7 @@
       </c>
       <c r="BA299" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="BB299" t="inlineStr">
@@ -55388,12 +55388,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -55427,13 +55427,13 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O300" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R300" t="n">
-        <v>0</v>
+        <v>0.09439766384661513</v>
       </c>
       <c r="S300" t="inlineStr">
         <is>
@@ -55442,7 +55442,7 @@
       </c>
       <c r="U300" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -55467,7 +55467,7 @@
       </c>
       <c r="AS300" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT300" t="n">
@@ -55485,7 +55485,7 @@
       </c>
       <c r="AW300" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX300" t="inlineStr">
@@ -55505,7 +55505,7 @@
       </c>
       <c r="BA300" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB300" t="inlineStr">
@@ -55547,12 +55547,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -55586,24 +55586,24 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O301" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U301" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V301" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W301" t="inlineStr">
         <is>
-          <t>SRC_SK_ECDC_ATLAS</t>
+          <t>SRC_SI_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X301" t="inlineStr">
@@ -55633,7 +55633,7 @@
       </c>
       <c r="AC301" t="inlineStr">
         <is>
-          <t>country:SK:national</t>
+          <t>country:SI:national</t>
         </is>
       </c>
       <c r="AD301" t="inlineStr">
@@ -55673,7 +55673,7 @@
       </c>
       <c r="AK301" t="inlineStr">
         <is>
-          <t>Slovakia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM301" t="inlineStr">
@@ -55701,7 +55701,7 @@
       </c>
       <c r="AS301" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT301" t="n">
@@ -55719,7 +55719,7 @@
       </c>
       <c r="AW301" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX301" t="inlineStr">
@@ -55739,7 +55739,7 @@
       </c>
       <c r="BA301" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB301" t="inlineStr">
@@ -55781,12 +55781,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -55820,84 +55820,95 @@
         </is>
       </c>
       <c r="N302" t="n">
+        <v>0</v>
+      </c>
+      <c r="O302" t="n">
+        <v>0</v>
+      </c>
+      <c r="R302" t="n">
+        <v>0</v>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO302" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP302" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ302" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS302" t="inlineStr">
+        <is>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT302" t="n">
         <v>1</v>
       </c>
-      <c r="O302" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
-      <c r="R302" t="n">
-        <v>0.004307752377642386</v>
-      </c>
-      <c r="S302" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO302" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP302" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR302" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS302" t="inlineStr"/>
-      <c r="AT302" t="n">
-        <v>0</v>
-      </c>
       <c r="AU302" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV302" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW302" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ302" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA302" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="BB302" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC302" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -55924,17 +55935,17 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -55959,93 +55970,179 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="N303" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="O303" t="n">
-        <v>510</v>
-      </c>
-      <c r="Q303" t="n">
         <v>0</v>
       </c>
-      <c r="R303" t="n">
-        <v>0.2405676564611412</v>
-      </c>
-      <c r="S303" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W303" t="inlineStr">
+        <is>
+          <t>SRC_SK_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X303" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y303" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z303" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB303" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC303" t="inlineStr">
+        <is>
+          <t>country:SK:national</t>
+        </is>
+      </c>
+      <c r="AD303" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE303" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF303" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG303" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH303" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI303" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ303" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK303" t="inlineStr">
+        <is>
+          <t>Slovakia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM303" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN303" t="b">
+        <v>1</v>
       </c>
       <c r="AO303" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP303" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR303" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS303" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ303" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS303" t="inlineStr">
+        <is>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV303" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ303" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA303" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="BB303" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC303" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -56107,25 +56204,25 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="N304" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O304" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q304" t="n">
         <v>0</v>
       </c>
       <c r="R304" t="n">
-        <v>0.008615504755284772</v>
+        <v>0.004307752377642386</v>
       </c>
       <c r="S304" t="inlineStr">
         <is>
@@ -56255,25 +56352,25 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="N305" t="n">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="O305" t="n">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="Q305" t="n">
         <v>0</v>
       </c>
       <c r="R305" t="n">
-        <v>0.2462280719072857</v>
+        <v>0.2405676564611412</v>
       </c>
       <c r="S305" t="inlineStr">
         <is>
@@ -56403,25 +56500,25 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="N306" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O306" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q306" t="n">
         <v>0</v>
       </c>
       <c r="R306" t="n">
-        <v>0.004307752377642386</v>
+        <v>0.008615504755284772</v>
       </c>
       <c r="S306" t="inlineStr">
         <is>
@@ -56551,25 +56648,25 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="N307" t="n">
-        <v>636</v>
+        <v>522</v>
       </c>
       <c r="O307" t="n">
-        <v>636</v>
+        <v>522</v>
       </c>
       <c r="Q307" t="n">
         <v>0</v>
       </c>
       <c r="R307" t="n">
-        <v>0.3000020186456585</v>
+        <v>0.2462280719072857</v>
       </c>
       <c r="S307" t="inlineStr">
         <is>
@@ -56669,12 +56766,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -56699,25 +56796,25 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="N308" t="n">
-        <v>612</v>
+        <v>1</v>
       </c>
       <c r="O308" t="n">
-        <v>612</v>
+        <v>1</v>
       </c>
       <c r="Q308" t="n">
         <v>0</v>
       </c>
       <c r="R308" t="n">
-        <v>0.2886811877533695</v>
+        <v>0.004307752377642386</v>
       </c>
       <c r="S308" t="inlineStr">
         <is>
@@ -56750,42 +56847,42 @@
       </c>
       <c r="AV308" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW308" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ308" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA308" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB308" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC308" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -56817,12 +56914,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -56847,25 +56944,25 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="N309" t="n">
-        <v>4</v>
+        <v>636</v>
       </c>
       <c r="O309" t="n">
-        <v>4</v>
+        <v>636</v>
       </c>
       <c r="Q309" t="n">
         <v>0</v>
       </c>
       <c r="R309" t="n">
-        <v>0.01723100951056954</v>
+        <v>0.3000020186456585</v>
       </c>
       <c r="S309" t="inlineStr">
         <is>
@@ -56898,42 +56995,42 @@
       </c>
       <c r="AV309" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ309" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA309" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB309" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC309" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -56995,25 +57092,25 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="N310" t="n">
-        <v>655</v>
+        <v>612</v>
       </c>
       <c r="O310" t="n">
-        <v>655</v>
+        <v>612</v>
       </c>
       <c r="Q310" t="n">
         <v>0</v>
       </c>
       <c r="R310" t="n">
-        <v>0.308964343102054</v>
+        <v>0.2886811877533695</v>
       </c>
       <c r="S310" t="inlineStr">
         <is>
@@ -57113,12 +57210,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -57143,25 +57240,25 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="N311" t="n">
-        <v>727</v>
+        <v>4</v>
       </c>
       <c r="O311" t="n">
-        <v>727</v>
+        <v>4</v>
       </c>
       <c r="Q311" t="n">
         <v>0</v>
       </c>
       <c r="R311" t="n">
-        <v>0.3429268357789209</v>
+        <v>0.01723100951056954</v>
       </c>
       <c r="S311" t="inlineStr">
         <is>
@@ -57194,42 +57291,42 @@
       </c>
       <c r="AV311" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ311" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA311" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB311" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC311" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -57261,12 +57358,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -57291,25 +57388,25 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="N312" t="n">
-        <v>1</v>
+        <v>655</v>
       </c>
       <c r="O312" t="n">
-        <v>1</v>
+        <v>655</v>
       </c>
       <c r="Q312" t="n">
         <v>0</v>
       </c>
       <c r="R312" t="n">
-        <v>0.004307752377642386</v>
+        <v>0.308964343102054</v>
       </c>
       <c r="S312" t="inlineStr">
         <is>
@@ -57342,42 +57439,42 @@
       </c>
       <c r="AV312" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ312" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA312" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB312" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC312" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -57439,25 +57536,25 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="N313" t="n">
-        <v>738</v>
+        <v>727</v>
       </c>
       <c r="O313" t="n">
-        <v>738</v>
+        <v>727</v>
       </c>
       <c r="Q313" t="n">
         <v>0</v>
       </c>
       <c r="R313" t="n">
-        <v>0.3481155499378867</v>
+        <v>0.3429268357789209</v>
       </c>
       <c r="S313" t="inlineStr">
         <is>
@@ -57587,25 +57684,25 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="N314" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O314" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q314" t="n">
         <v>0</v>
       </c>
       <c r="R314" t="n">
-        <v>0.008615504755284772</v>
+        <v>0.004307752377642386</v>
       </c>
       <c r="S314" t="inlineStr">
         <is>
@@ -57735,25 +57832,25 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="N315" t="n">
-        <v>678</v>
+        <v>738</v>
       </c>
       <c r="O315" t="n">
-        <v>678</v>
+        <v>738</v>
       </c>
       <c r="Q315" t="n">
         <v>0</v>
       </c>
       <c r="R315" t="n">
-        <v>0.3198134727071642</v>
+        <v>0.3481155499378867</v>
       </c>
       <c r="S315" t="inlineStr">
         <is>
@@ -57853,12 +57950,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -57883,25 +57980,25 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="N316" t="n">
-        <v>707</v>
+        <v>2</v>
       </c>
       <c r="O316" t="n">
-        <v>707</v>
+        <v>2</v>
       </c>
       <c r="Q316" t="n">
         <v>0</v>
       </c>
       <c r="R316" t="n">
-        <v>0.3334928100353468</v>
+        <v>0.008615504755284772</v>
       </c>
       <c r="S316" t="inlineStr">
         <is>
@@ -57934,42 +58031,42 @@
       </c>
       <c r="AV316" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW316" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX316" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY316" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ316" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA316" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB316" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC316" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -58031,25 +58128,25 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="N317" t="n">
-        <v>555</v>
+        <v>678</v>
       </c>
       <c r="O317" t="n">
-        <v>555</v>
+        <v>678</v>
       </c>
       <c r="Q317" t="n">
         <v>0</v>
       </c>
       <c r="R317" t="n">
-        <v>0.2617942143841831</v>
+        <v>0.3198134727071642</v>
       </c>
       <c r="S317" t="inlineStr">
         <is>
@@ -58149,12 +58246,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -58179,25 +58276,25 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="N318" t="n">
-        <v>1</v>
+        <v>707</v>
       </c>
       <c r="O318" t="n">
-        <v>1</v>
+        <v>707</v>
       </c>
       <c r="Q318" t="n">
         <v>0</v>
       </c>
       <c r="R318" t="n">
-        <v>0.004307752377642386</v>
+        <v>0.3334928100353468</v>
       </c>
       <c r="S318" t="inlineStr">
         <is>
@@ -58230,42 +58327,42 @@
       </c>
       <c r="AV318" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW318" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX318" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY318" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ318" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA318" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB318" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC318" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -58327,25 +58424,25 @@
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="N319" t="n">
-        <v>494</v>
+        <v>555</v>
       </c>
       <c r="O319" t="n">
-        <v>494</v>
+        <v>555</v>
       </c>
       <c r="Q319" t="n">
         <v>0</v>
       </c>
       <c r="R319" t="n">
-        <v>0.2330204358662819</v>
+        <v>0.2617942143841831</v>
       </c>
       <c r="S319" t="inlineStr">
         <is>
@@ -58475,12 +58572,12 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="N320" t="n">
@@ -58623,25 +58720,25 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="N321" t="n">
-        <v>602</v>
+        <v>494</v>
       </c>
       <c r="O321" t="n">
-        <v>602</v>
+        <v>494</v>
       </c>
       <c r="Q321" t="n">
         <v>0</v>
       </c>
       <c r="R321" t="n">
-        <v>0.282878246688674</v>
+        <v>0.2330204358662819</v>
       </c>
       <c r="S321" t="inlineStr">
         <is>
@@ -58771,12 +58868,12 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="N322" t="n">
@@ -58789,7 +58886,7 @@
         <v>0</v>
       </c>
       <c r="R322" t="n">
-        <v>0.004326608212170636</v>
+        <v>0.004307752377642386</v>
       </c>
       <c r="S322" t="inlineStr">
         <is>
@@ -58919,25 +59016,25 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N323" t="n">
-        <v>578</v>
+        <v>602</v>
       </c>
       <c r="O323" t="n">
-        <v>578</v>
+        <v>602</v>
       </c>
       <c r="Q323" t="n">
         <v>0</v>
       </c>
       <c r="R323" t="n">
-        <v>0.2716007086147069</v>
+        <v>0.282878246688674</v>
       </c>
       <c r="S323" t="inlineStr">
         <is>
@@ -59037,12 +59134,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -59067,93 +59164,104 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N324" t="n">
-        <v>590</v>
+        <v>9</v>
       </c>
       <c r="O324" t="n">
-        <v>590</v>
-      </c>
-      <c r="Q324" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R324" t="n">
-        <v>0.2772394776516905</v>
+        <v>0.01879308392794999</v>
       </c>
       <c r="S324" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO324" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP324" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR324" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS324" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ324" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS324" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU324" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV324" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW324" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY324" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ324" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA324" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB324" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC324" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -59180,17 +59288,17 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -59215,93 +59323,179 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N325" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O325" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q325" t="n">
-        <v>0</v>
-      </c>
-      <c r="R325" t="n">
-        <v>0.008653216424341272</v>
-      </c>
-      <c r="S325" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W325" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X325" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y325" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z325" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB325" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC325" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD325" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE325" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF325" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG325" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH325" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI325" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ325" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK325" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM325" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN325" t="b">
+        <v>1</v>
       </c>
       <c r="AO325" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP325" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR325" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS325" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ325" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS325" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU325" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV325" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW325" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX325" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY325" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ325" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA325" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB325" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC325" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -59333,12 +59527,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -59363,93 +59557,104 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N326" t="n">
-        <v>652</v>
+        <v>2</v>
       </c>
       <c r="O326" t="n">
-        <v>652</v>
-      </c>
-      <c r="Q326" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R326" t="n">
-        <v>0.3063731176761054</v>
+        <v>0.02012306360160882</v>
       </c>
       <c r="S326" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO326" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP326" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR326" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS326" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ326" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS326" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU326" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV326" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW326" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX326" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY326" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ326" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA326" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB326" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC326" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -59476,17 +59681,17 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -59511,93 +59716,179 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N327" t="n">
+        <v>2</v>
+      </c>
+      <c r="O327" t="n">
+        <v>2</v>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W327" t="inlineStr">
+        <is>
+          <t>SRC_GR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X327" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z327" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB327" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC327" t="inlineStr">
+        <is>
+          <t>country:GR:national</t>
+        </is>
+      </c>
+      <c r="AD327" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE327" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF327" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG327" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH327" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI327" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ327" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK327" t="inlineStr">
+        <is>
+          <t>Greece annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM327" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN327" t="b">
         <v>1</v>
       </c>
-      <c r="O327" t="n">
+      <c r="AO327" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP327" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ327" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS327" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT327" t="n">
         <v>1</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
-      <c r="R327" t="n">
-        <v>0.004326608212170636</v>
-      </c>
-      <c r="S327" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO327" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP327" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR327" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS327" t="inlineStr"/>
-      <c r="AT327" t="n">
-        <v>0</v>
-      </c>
       <c r="AU327" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV327" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW327" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX327" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY327" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ327" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA327" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB327" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC327" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -59629,12 +59920,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -59659,93 +59950,104 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N328" t="n">
-        <v>588</v>
+        <v>2</v>
       </c>
       <c r="O328" t="n">
-        <v>588</v>
-      </c>
-      <c r="Q328" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R328" t="n">
-        <v>0.2762996828121932</v>
+        <v>0.02076350092143226</v>
       </c>
       <c r="S328" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO328" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP328" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR328" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS328" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ328" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS328" t="inlineStr">
+        <is>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU328" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV328" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW328" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX328" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY328" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ328" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA328" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB328" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC328" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -59772,17 +60074,17 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -59807,12 +60109,12 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N329" t="n">
@@ -59821,79 +60123,165 @@
       <c r="O329" t="n">
         <v>2</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
-      <c r="R329" t="n">
-        <v>0.008653216424341272</v>
-      </c>
-      <c r="S329" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W329" t="inlineStr">
+        <is>
+          <t>SRC_HU_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X329" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z329" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB329" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC329" t="inlineStr">
+        <is>
+          <t>country:HU:national</t>
+        </is>
+      </c>
+      <c r="AD329" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE329" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF329" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG329" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH329" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI329" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ329" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK329" t="inlineStr">
+        <is>
+          <t>Hungary annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM329" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN329" t="b">
+        <v>1</v>
       </c>
       <c r="AO329" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP329" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR329" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS329" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ329" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS329" t="inlineStr">
+        <is>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU329" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV329" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW329" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX329" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY329" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ329" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA329" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB329" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC329" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -59920,17 +60308,17 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -59955,93 +60343,184 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N330" t="n">
-        <v>586</v>
+        <v>0</v>
       </c>
       <c r="O330" t="n">
-        <v>586</v>
-      </c>
-      <c r="Q330" t="n">
         <v>0</v>
       </c>
-      <c r="R330" t="n">
-        <v>0.2753598879726959</v>
-      </c>
-      <c r="S330" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W330" t="inlineStr">
+        <is>
+          <t>SRC_IS_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X330" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y330" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z330" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB330" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC330" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD330" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE330" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF330" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG330" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH330" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI330" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ330" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK330" t="inlineStr">
+        <is>
+          <t>Iceland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM330" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN330" t="b">
+        <v>0</v>
       </c>
       <c r="AO330" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP330" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ330" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR330" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS330" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS330" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT330" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU330" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV330" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW330" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY330" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ330" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA330" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB330" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC330" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -60073,12 +60552,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -60103,93 +60582,104 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N331" t="n">
+        <v>0</v>
+      </c>
+      <c r="O331" t="n">
+        <v>0</v>
+      </c>
+      <c r="R331" t="n">
+        <v>0</v>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO331" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP331" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ331" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS331" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT331" t="n">
         <v>1</v>
       </c>
-      <c r="O331" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q331" t="n">
-        <v>0</v>
-      </c>
-      <c r="R331" t="n">
-        <v>0.004326608212170636</v>
-      </c>
-      <c r="S331" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO331" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP331" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR331" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS331" t="inlineStr"/>
-      <c r="AT331" t="n">
-        <v>0</v>
-      </c>
       <c r="AU331" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV331" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW331" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="AX331" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY331" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ331" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA331" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="BB331" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC331" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -60216,17 +60706,17 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -60251,93 +60741,179 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N332" t="n">
-        <v>635</v>
+        <v>0</v>
       </c>
       <c r="O332" t="n">
-        <v>635</v>
-      </c>
-      <c r="Q332" t="n">
         <v>0</v>
       </c>
-      <c r="R332" t="n">
-        <v>0.2983848615403787</v>
-      </c>
-      <c r="S332" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W332" t="inlineStr">
+        <is>
+          <t>SRC_RO_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X332" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y332" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z332" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB332" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC332" t="inlineStr">
+        <is>
+          <t>country:RO:national</t>
+        </is>
+      </c>
+      <c r="AD332" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE332" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF332" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG332" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH332" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI332" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ332" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK332" t="inlineStr">
+        <is>
+          <t>Romania annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM332" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN332" t="b">
+        <v>1</v>
       </c>
       <c r="AO332" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP332" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR332" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS332" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ332" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS332" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU332" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV332" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW332" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="AX332" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY332" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ332" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA332" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="BB332" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC332" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -60369,12 +60945,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -60399,12 +60975,12 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N333" t="n">
@@ -60413,79 +60989,90 @@
       <c r="O333" t="n">
         <v>3</v>
       </c>
-      <c r="Q333" t="n">
-        <v>0</v>
-      </c>
       <c r="R333" t="n">
-        <v>0.01297982463651191</v>
+        <v>0.1417051474867175</v>
       </c>
       <c r="S333" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO333" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP333" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR333" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS333" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ333" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS333" t="inlineStr">
+        <is>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT333" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU333" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV333" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW333" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX333" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY333" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ333" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA333" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB333" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC333" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -60512,17 +61099,17 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -60547,93 +61134,179 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N334" t="n">
-        <v>646</v>
+        <v>3</v>
       </c>
       <c r="O334" t="n">
-        <v>646</v>
-      </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
-      <c r="R334" t="n">
-        <v>0.3035537331576136</v>
-      </c>
-      <c r="S334" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W334" t="inlineStr">
+        <is>
+          <t>SRC_SI_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X334" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y334" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z334" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB334" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC334" t="inlineStr">
+        <is>
+          <t>country:SI:national</t>
+        </is>
+      </c>
+      <c r="AD334" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE334" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF334" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG334" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH334" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI334" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ334" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK334" t="inlineStr">
+        <is>
+          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM334" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN334" t="b">
+        <v>1</v>
       </c>
       <c r="AO334" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP334" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR334" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS334" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ334" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS334" t="inlineStr">
+        <is>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU334" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV334" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW334" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX334" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY334" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ334" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA334" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB334" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC334" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -60665,12 +61338,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -60695,93 +61368,104 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N335" t="n">
+        <v>2</v>
+      </c>
+      <c r="O335" t="n">
+        <v>2</v>
+      </c>
+      <c r="R335" t="n">
+        <v>0.03653047436099524</v>
+      </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO335" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP335" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ335" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS335" t="inlineStr">
+        <is>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT335" t="n">
         <v>1</v>
       </c>
-      <c r="O335" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
-      <c r="R335" t="n">
-        <v>0.004326608212170636</v>
-      </c>
-      <c r="S335" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO335" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP335" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR335" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS335" t="inlineStr"/>
-      <c r="AT335" t="n">
-        <v>0</v>
-      </c>
       <c r="AU335" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV335" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW335" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="AX335" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY335" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ335" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA335" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="BB335" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC335" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -60808,17 +61492,17 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -60843,93 +61527,179 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N336" t="n">
-        <v>678</v>
+        <v>2</v>
       </c>
       <c r="O336" t="n">
-        <v>678</v>
-      </c>
-      <c r="Q336" t="n">
-        <v>0</v>
-      </c>
-      <c r="R336" t="n">
-        <v>0.3185904505895697</v>
-      </c>
-      <c r="S336" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W336" t="inlineStr">
+        <is>
+          <t>SRC_SK_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X336" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y336" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z336" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB336" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC336" t="inlineStr">
+        <is>
+          <t>country:SK:national</t>
+        </is>
+      </c>
+      <c r="AD336" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE336" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF336" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG336" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH336" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI336" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ336" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK336" t="inlineStr">
+        <is>
+          <t>Slovakia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM336" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN336" t="b">
+        <v>1</v>
       </c>
       <c r="AO336" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP336" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR336" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS336" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ336" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS336" t="inlineStr">
+        <is>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU336" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV336" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW336" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="AX336" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY336" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ336" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA336" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="BB336" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC336" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -60991,12 +61761,12 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N337" t="n">
@@ -61139,25 +61909,25 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="N338" t="n">
-        <v>695</v>
+        <v>578</v>
       </c>
       <c r="O338" t="n">
-        <v>695</v>
+        <v>578</v>
       </c>
       <c r="Q338" t="n">
         <v>0</v>
       </c>
       <c r="R338" t="n">
-        <v>0.3265787067252964</v>
+        <v>0.2716007086147069</v>
       </c>
       <c r="S338" t="inlineStr">
         <is>
@@ -61257,12 +62027,12 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -61287,25 +62057,25 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="N339" t="n">
-        <v>3</v>
+        <v>590</v>
       </c>
       <c r="O339" t="n">
-        <v>3</v>
+        <v>590</v>
       </c>
       <c r="Q339" t="n">
         <v>0</v>
       </c>
       <c r="R339" t="n">
-        <v>0.01297982463651191</v>
+        <v>0.2772394776516905</v>
       </c>
       <c r="S339" t="inlineStr">
         <is>
@@ -61338,42 +62108,42 @@
       </c>
       <c r="AV339" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW339" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX339" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY339" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ339" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA339" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB339" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC339" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -61405,12 +62175,12 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -61435,25 +62205,25 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="N340" t="n">
-        <v>565</v>
+        <v>2</v>
       </c>
       <c r="O340" t="n">
-        <v>565</v>
+        <v>2</v>
       </c>
       <c r="Q340" t="n">
         <v>0</v>
       </c>
       <c r="R340" t="n">
-        <v>0.2654920421579747</v>
+        <v>0.008653216424341272</v>
       </c>
       <c r="S340" t="inlineStr">
         <is>
@@ -61486,42 +62256,42 @@
       </c>
       <c r="AV340" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW340" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX340" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY340" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ340" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA340" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB340" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC340" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -61553,12 +62323,12 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -61583,25 +62353,25 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="N341" t="n">
-        <v>2</v>
+        <v>652</v>
       </c>
       <c r="O341" t="n">
-        <v>2</v>
+        <v>652</v>
       </c>
       <c r="Q341" t="n">
         <v>0</v>
       </c>
       <c r="R341" t="n">
-        <v>0.008653216424341272</v>
+        <v>0.3063731176761054</v>
       </c>
       <c r="S341" t="inlineStr">
         <is>
@@ -61634,42 +62404,42 @@
       </c>
       <c r="AV341" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW341" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX341" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY341" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ341" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA341" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB341" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC341" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -61701,12 +62471,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -61731,25 +62501,25 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="N342" t="n">
-        <v>464</v>
+        <v>1</v>
       </c>
       <c r="O342" t="n">
-        <v>464</v>
+        <v>1</v>
       </c>
       <c r="Q342" t="n">
         <v>0</v>
       </c>
       <c r="R342" t="n">
-        <v>0.2180324027633633</v>
+        <v>0.004326608212170636</v>
       </c>
       <c r="S342" t="inlineStr">
         <is>
@@ -61782,42 +62552,42 @@
       </c>
       <c r="AV342" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW342" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX342" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY342" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ342" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA342" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB342" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC342" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -61849,12 +62619,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -61879,25 +62649,25 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="N343" t="n">
-        <v>3</v>
+        <v>588</v>
       </c>
       <c r="O343" t="n">
-        <v>3</v>
+        <v>588</v>
       </c>
       <c r="Q343" t="n">
         <v>0</v>
       </c>
       <c r="R343" t="n">
-        <v>0.01297982463651191</v>
+        <v>0.2762996828121932</v>
       </c>
       <c r="S343" t="inlineStr">
         <is>
@@ -61930,40 +62700,2260 @@
       </c>
       <c r="AV343" t="inlineStr">
         <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW343" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX343" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY343" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA343" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB343" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC343" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="N344" t="n">
+        <v>2</v>
+      </c>
+      <c r="O344" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q344" t="n">
+        <v>0</v>
+      </c>
+      <c r="R344" t="n">
+        <v>0.008653216424341272</v>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO344" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP344" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR344" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS344" t="inlineStr"/>
+      <c r="AT344" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU344" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV344" t="inlineStr">
+        <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="AW343" t="inlineStr">
+      <c r="AW344" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="AX343" t="inlineStr">
+      <c r="AX344" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="AY343" t="inlineStr">
+      <c r="AY344" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="AZ343" t="inlineStr">
+      <c r="AZ344" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="BA343" t="inlineStr">
+      <c r="BA344" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="BB343" t="inlineStr">
+      <c r="BB344" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="BC343" t="inlineStr">
+      <c r="BC344" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="N345" t="n">
+        <v>586</v>
+      </c>
+      <c r="O345" t="n">
+        <v>586</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>0</v>
+      </c>
+      <c r="R345" t="n">
+        <v>0.2753598879726959</v>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO345" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP345" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR345" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS345" t="inlineStr"/>
+      <c r="AT345" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU345" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV345" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW345" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX345" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY345" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA345" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB345" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC345" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="N346" t="n">
+        <v>1</v>
+      </c>
+      <c r="O346" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q346" t="n">
+        <v>0</v>
+      </c>
+      <c r="R346" t="n">
+        <v>0.004326608212170636</v>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO346" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP346" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR346" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS346" t="inlineStr"/>
+      <c r="AT346" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU346" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV346" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW346" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX346" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY346" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA346" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB346" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC346" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="N347" t="n">
+        <v>635</v>
+      </c>
+      <c r="O347" t="n">
+        <v>635</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>0</v>
+      </c>
+      <c r="R347" t="n">
+        <v>0.2983848615403787</v>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO347" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP347" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR347" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS347" t="inlineStr"/>
+      <c r="AT347" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU347" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV347" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW347" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX347" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY347" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA347" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB347" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC347" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="N348" t="n">
+        <v>3</v>
+      </c>
+      <c r="O348" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>0</v>
+      </c>
+      <c r="R348" t="n">
+        <v>0.01297982463651191</v>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO348" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP348" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR348" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS348" t="inlineStr"/>
+      <c r="AT348" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU348" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV348" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW348" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX348" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY348" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA348" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB348" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC348" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="N349" t="n">
+        <v>646</v>
+      </c>
+      <c r="O349" t="n">
+        <v>646</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>0</v>
+      </c>
+      <c r="R349" t="n">
+        <v>0.3035537331576136</v>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO349" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP349" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR349" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS349" t="inlineStr"/>
+      <c r="AT349" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU349" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV349" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW349" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX349" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY349" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA349" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB349" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC349" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="N350" t="n">
+        <v>1</v>
+      </c>
+      <c r="O350" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>0</v>
+      </c>
+      <c r="R350" t="n">
+        <v>0.004326608212170636</v>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO350" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP350" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR350" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS350" t="inlineStr"/>
+      <c r="AT350" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU350" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV350" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW350" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX350" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY350" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA350" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB350" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC350" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="N351" t="n">
+        <v>678</v>
+      </c>
+      <c r="O351" t="n">
+        <v>678</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>0</v>
+      </c>
+      <c r="R351" t="n">
+        <v>0.3185904505895697</v>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO351" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP351" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR351" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS351" t="inlineStr"/>
+      <c r="AT351" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU351" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV351" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW351" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX351" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY351" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA351" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB351" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC351" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="N352" t="n">
+        <v>1</v>
+      </c>
+      <c r="O352" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>0</v>
+      </c>
+      <c r="R352" t="n">
+        <v>0.004326608212170636</v>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO352" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP352" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR352" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS352" t="inlineStr"/>
+      <c r="AT352" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU352" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV352" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW352" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX352" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY352" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA352" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB352" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC352" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="N353" t="n">
+        <v>695</v>
+      </c>
+      <c r="O353" t="n">
+        <v>695</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>0</v>
+      </c>
+      <c r="R353" t="n">
+        <v>0.3265787067252964</v>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO353" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP353" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR353" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS353" t="inlineStr"/>
+      <c r="AT353" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU353" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV353" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW353" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX353" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY353" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA353" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB353" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC353" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="N354" t="n">
+        <v>3</v>
+      </c>
+      <c r="O354" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>0</v>
+      </c>
+      <c r="R354" t="n">
+        <v>0.01297982463651191</v>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO354" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP354" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR354" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS354" t="inlineStr"/>
+      <c r="AT354" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU354" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV354" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW354" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX354" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY354" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA354" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB354" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC354" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="N355" t="n">
+        <v>565</v>
+      </c>
+      <c r="O355" t="n">
+        <v>565</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>0</v>
+      </c>
+      <c r="R355" t="n">
+        <v>0.2654920421579747</v>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO355" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP355" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR355" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS355" t="inlineStr"/>
+      <c r="AT355" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU355" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV355" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW355" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX355" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY355" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA355" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB355" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC355" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="N356" t="n">
+        <v>2</v>
+      </c>
+      <c r="O356" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>0</v>
+      </c>
+      <c r="R356" t="n">
+        <v>0.008653216424341272</v>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO356" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP356" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR356" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS356" t="inlineStr"/>
+      <c r="AT356" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU356" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV356" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW356" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX356" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY356" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA356" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB356" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC356" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="N357" t="n">
+        <v>464</v>
+      </c>
+      <c r="O357" t="n">
+        <v>464</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>0</v>
+      </c>
+      <c r="R357" t="n">
+        <v>0.2180324027633633</v>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO357" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP357" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR357" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS357" t="inlineStr"/>
+      <c r="AT357" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU357" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV357" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW357" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX357" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY357" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA357" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB357" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC357" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="N358" t="n">
+        <v>3</v>
+      </c>
+      <c r="O358" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>0</v>
+      </c>
+      <c r="R358" t="n">
+        <v>0.01297982463651191</v>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO358" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP358" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR358" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS358" t="inlineStr"/>
+      <c r="AT358" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU358" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV358" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW358" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX358" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY358" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA358" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB358" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC358" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -62085,7 +65075,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
@@ -62095,7 +65085,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11">
@@ -62115,7 +65105,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13">
@@ -62125,7 +65115,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -62147,7 +65137,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33576</v>
+        <v>33709</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d085/2020-2025.xlsx
+++ b/diseases/d085/2020-2025.xlsx
@@ -58986,12 +58986,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -59025,84 +59025,95 @@
         </is>
       </c>
       <c r="N323" t="n">
-        <v>602</v>
+        <v>0</v>
       </c>
       <c r="O323" t="n">
-        <v>602</v>
-      </c>
-      <c r="Q323" t="n">
         <v>0</v>
       </c>
       <c r="R323" t="n">
-        <v>0.282878246688674</v>
+        <v>0</v>
       </c>
       <c r="S323" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>SER_BG_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO323" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP323" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR323" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS323" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ323" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS323" t="inlineStr">
+        <is>
+          <t>SER_BG_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU323" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV323" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW323" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
         </is>
       </c>
       <c r="AX323" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY323" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ323" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA323" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
         </is>
       </c>
       <c r="BB323" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC323" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -59129,17 +59140,17 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -59173,22 +59184,39 @@
         </is>
       </c>
       <c r="N324" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O324" t="n">
-        <v>9</v>
-      </c>
-      <c r="R324" t="n">
-        <v>0.01879308392794999</v>
-      </c>
-      <c r="S324" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U324" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
+          <t>SER_BG_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>SER_BG_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W324" t="inlineStr">
+        <is>
+          <t>SRC_BG_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X324" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y324" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z324" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -59196,6 +59224,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB324" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC324" t="inlineStr">
+        <is>
+          <t>country:BG:national</t>
+        </is>
+      </c>
+      <c r="AD324" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE324" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF324" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG324" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH324" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI324" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ324" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK324" t="inlineStr">
+        <is>
+          <t>Bulgaria annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM324" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN324" t="b">
+        <v>1</v>
+      </c>
       <c r="AO324" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -59213,7 +59299,7 @@
       </c>
       <c r="AS324" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
+          <t>SER_BG_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT324" t="n">
@@ -59231,7 +59317,7 @@
       </c>
       <c r="AW324" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
         </is>
       </c>
       <c r="AX324" t="inlineStr">
@@ -59251,7 +59337,7 @@
       </c>
       <c r="BA324" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
         </is>
       </c>
       <c r="BB324" t="inlineStr">
@@ -59288,17 +59374,17 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -59332,170 +59418,84 @@
         </is>
       </c>
       <c r="N325" t="n">
-        <v>9</v>
+        <v>602</v>
       </c>
       <c r="O325" t="n">
-        <v>9</v>
-      </c>
-      <c r="U325" t="inlineStr">
-        <is>
-          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V325" t="inlineStr">
-        <is>
-          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W325" t="inlineStr">
-        <is>
-          <t>SRC_ES_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X325" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis, congenital</t>
-        </is>
-      </c>
-      <c r="Y325" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z325" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
-      <c r="AA325" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB325" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC325" t="inlineStr">
-        <is>
-          <t>country:ES:national</t>
-        </is>
-      </c>
-      <c r="AD325" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE325" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF325" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG325" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH325" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI325" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ325" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK325" t="inlineStr">
-        <is>
-          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM325" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN325" t="b">
-        <v>1</v>
+        <v>602</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>0</v>
+      </c>
+      <c r="R325" t="n">
+        <v>0.282878246688674</v>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO325" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP325" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ325" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS325" t="inlineStr">
-        <is>
-          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR325" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS325" t="inlineStr"/>
       <c r="AT325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU325" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV325" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW325" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX325" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY325" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ325" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA325" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB325" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC325" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -59527,12 +59527,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -59566,13 +59566,13 @@
         </is>
       </c>
       <c r="N326" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O326" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R326" t="n">
-        <v>0.02012306360160882</v>
+        <v>0</v>
       </c>
       <c r="S326" t="inlineStr">
         <is>
@@ -59581,7 +59581,7 @@
       </c>
       <c r="U326" t="inlineStr">
         <is>
-          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_CY_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
@@ -59606,7 +59606,7 @@
       </c>
       <c r="AS326" t="inlineStr">
         <is>
-          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_CY_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT326" t="n">
@@ -59624,7 +59624,7 @@
       </c>
       <c r="AW326" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="AX326" t="inlineStr">
@@ -59644,7 +59644,7 @@
       </c>
       <c r="BA326" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="BB326" t="inlineStr">
@@ -59686,12 +59686,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -59725,24 +59725,24 @@
         </is>
       </c>
       <c r="N327" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O327" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U327" t="inlineStr">
         <is>
-          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_CY_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V327" t="inlineStr">
         <is>
-          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_CY_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W327" t="inlineStr">
         <is>
-          <t>SRC_GR_ECDC_ATLAS</t>
+          <t>SRC_CY_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X327" t="inlineStr">
@@ -59772,7 +59772,7 @@
       </c>
       <c r="AC327" t="inlineStr">
         <is>
-          <t>country:GR:national</t>
+          <t>country:CY:national</t>
         </is>
       </c>
       <c r="AD327" t="inlineStr">
@@ -59812,7 +59812,7 @@
       </c>
       <c r="AK327" t="inlineStr">
         <is>
-          <t>Greece annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Cyprus annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM327" t="inlineStr">
@@ -59840,7 +59840,7 @@
       </c>
       <c r="AS327" t="inlineStr">
         <is>
-          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_CY_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT327" t="n">
@@ -59858,7 +59858,7 @@
       </c>
       <c r="AW327" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="AX327" t="inlineStr">
@@ -59878,7 +59878,7 @@
       </c>
       <c r="BA327" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="BB327" t="inlineStr">
@@ -59920,12 +59920,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -59965,7 +59965,7 @@
         <v>2</v>
       </c>
       <c r="R328" t="n">
-        <v>0.02076350092143226</v>
+        <v>0.01885149260698658</v>
       </c>
       <c r="S328" t="inlineStr">
         <is>
@@ -59974,7 +59974,7 @@
       </c>
       <c r="U328" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_CZ_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -59999,7 +59999,7 @@
       </c>
       <c r="AS328" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_CZ_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT328" t="n">
@@ -60017,7 +60017,7 @@
       </c>
       <c r="AW328" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX328" t="inlineStr">
@@ -60037,7 +60037,7 @@
       </c>
       <c r="BA328" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB328" t="inlineStr">
@@ -60079,12 +60079,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -60125,17 +60125,17 @@
       </c>
       <c r="U329" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_CZ_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V329" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_CZ_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W329" t="inlineStr">
         <is>
-          <t>SRC_HU_ECDC_ATLAS</t>
+          <t>SRC_CZ_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X329" t="inlineStr">
@@ -60165,7 +60165,7 @@
       </c>
       <c r="AC329" t="inlineStr">
         <is>
-          <t>country:HU:national</t>
+          <t>country:CZ:national</t>
         </is>
       </c>
       <c r="AD329" t="inlineStr">
@@ -60205,7 +60205,7 @@
       </c>
       <c r="AK329" t="inlineStr">
         <is>
-          <t>Hungary annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Czechia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM329" t="inlineStr">
@@ -60233,7 +60233,7 @@
       </c>
       <c r="AS329" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_CZ_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT329" t="n">
@@ -60251,7 +60251,7 @@
       </c>
       <c r="AW329" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX329" t="inlineStr">
@@ -60271,7 +60271,7 @@
       </c>
       <c r="BA329" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB329" t="inlineStr">
@@ -60308,17 +60308,17 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -60357,34 +60357,17 @@
       <c r="O330" t="n">
         <v>0</v>
       </c>
+      <c r="R330" t="n">
+        <v>0</v>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U330" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V330" t="inlineStr">
-        <is>
-          <t>SER_IS_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W330" t="inlineStr">
-        <is>
-          <t>SRC_IS_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X330" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis, congenital</t>
-        </is>
-      </c>
-      <c r="Y330" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z330" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
@@ -60392,64 +60375,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB330" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC330" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD330" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE330" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF330" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG330" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH330" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI330" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ330" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK330" t="inlineStr">
-        <is>
-          <t>Iceland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM330" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN330" t="b">
-        <v>0</v>
-      </c>
       <c r="AO330" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -60457,7 +60382,7 @@
       </c>
       <c r="AP330" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ330" t="inlineStr">
@@ -60465,62 +60390,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR330" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS330" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT330" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU330" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV330" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW330" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY330" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ330" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA330" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="BB330" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC330" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -60547,17 +60467,17 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -60596,17 +60516,34 @@
       <c r="O331" t="n">
         <v>0</v>
       </c>
-      <c r="R331" t="n">
-        <v>0</v>
-      </c>
-      <c r="S331" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U331" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W331" t="inlineStr">
+        <is>
+          <t>SRC_EE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X331" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y331" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z331" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -60614,6 +60551,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB331" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC331" t="inlineStr">
+        <is>
+          <t>country:EE:national</t>
+        </is>
+      </c>
+      <c r="AD331" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE331" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF331" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG331" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH331" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI331" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ331" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK331" t="inlineStr">
+        <is>
+          <t>Estonia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM331" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN331" t="b">
+        <v>1</v>
+      </c>
       <c r="AO331" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -60631,7 +60626,7 @@
       </c>
       <c r="AS331" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT331" t="n">
@@ -60649,7 +60644,7 @@
       </c>
       <c r="AW331" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="AX331" t="inlineStr">
@@ -60669,7 +60664,7 @@
       </c>
       <c r="BA331" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="BB331" t="inlineStr">
@@ -60706,17 +60701,17 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -60750,39 +60745,22 @@
         </is>
       </c>
       <c r="N332" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O332" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="R332" t="n">
+        <v>0.01879308392794999</v>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U332" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V332" t="inlineStr">
-        <is>
-          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W332" t="inlineStr">
-        <is>
-          <t>SRC_RO_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X332" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis, congenital</t>
-        </is>
-      </c>
-      <c r="Y332" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z332" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -60790,64 +60768,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB332" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC332" t="inlineStr">
-        <is>
-          <t>country:RO:national</t>
-        </is>
-      </c>
-      <c r="AD332" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE332" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF332" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG332" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH332" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI332" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ332" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK332" t="inlineStr">
-        <is>
-          <t>Romania annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM332" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN332" t="b">
-        <v>1</v>
-      </c>
       <c r="AO332" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -60865,7 +60785,7 @@
       </c>
       <c r="AS332" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT332" t="n">
@@ -60883,7 +60803,7 @@
       </c>
       <c r="AW332" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX332" t="inlineStr">
@@ -60903,7 +60823,7 @@
       </c>
       <c r="BA332" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB332" t="inlineStr">
@@ -60940,17 +60860,17 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -60984,22 +60904,39 @@
         </is>
       </c>
       <c r="N333" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O333" t="n">
-        <v>3</v>
-      </c>
-      <c r="R333" t="n">
-        <v>0.1417051474867175</v>
-      </c>
-      <c r="S333" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="U333" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W333" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X333" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z333" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -61007,6 +60944,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB333" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC333" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD333" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE333" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF333" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG333" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH333" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI333" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ333" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK333" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM333" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN333" t="b">
+        <v>1</v>
+      </c>
       <c r="AO333" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -61024,7 +61019,7 @@
       </c>
       <c r="AS333" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT333" t="n">
@@ -61042,7 +61037,7 @@
       </c>
       <c r="AW333" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX333" t="inlineStr">
@@ -61062,7 +61057,7 @@
       </c>
       <c r="BA333" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB333" t="inlineStr">
@@ -61099,17 +61094,17 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -61143,39 +61138,22 @@
         </is>
       </c>
       <c r="N334" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O334" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="R334" t="n">
+        <v>0.02012306360160882</v>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U334" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V334" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W334" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X334" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis, congenital</t>
-        </is>
-      </c>
-      <c r="Y334" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z334" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -61183,64 +61161,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB334" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC334" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD334" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE334" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF334" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG334" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH334" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI334" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ334" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK334" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM334" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN334" t="b">
-        <v>1</v>
-      </c>
       <c r="AO334" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -61258,7 +61178,7 @@
       </c>
       <c r="AS334" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT334" t="n">
@@ -61276,7 +61196,7 @@
       </c>
       <c r="AW334" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX334" t="inlineStr">
@@ -61296,7 +61216,7 @@
       </c>
       <c r="BA334" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB334" t="inlineStr">
@@ -61333,17 +61253,17 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -61382,17 +61302,34 @@
       <c r="O335" t="n">
         <v>2</v>
       </c>
-      <c r="R335" t="n">
-        <v>0.03653047436099524</v>
-      </c>
-      <c r="S335" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U335" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W335" t="inlineStr">
+        <is>
+          <t>SRC_GR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X335" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z335" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
@@ -61400,6 +61337,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB335" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC335" t="inlineStr">
+        <is>
+          <t>country:GR:national</t>
+        </is>
+      </c>
+      <c r="AD335" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE335" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF335" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG335" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH335" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI335" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ335" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK335" t="inlineStr">
+        <is>
+          <t>Greece annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM335" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN335" t="b">
+        <v>1</v>
+      </c>
       <c r="AO335" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -61417,7 +61412,7 @@
       </c>
       <c r="AS335" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT335" t="n">
@@ -61435,7 +61430,7 @@
       </c>
       <c r="AW335" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX335" t="inlineStr">
@@ -61455,7 +61450,7 @@
       </c>
       <c r="BA335" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB335" t="inlineStr">
@@ -61492,17 +61487,17 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -61536,39 +61531,22 @@
         </is>
       </c>
       <c r="N336" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O336" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="R336" t="n">
+        <v>0</v>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U336" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V336" t="inlineStr">
-        <is>
-          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W336" t="inlineStr">
-        <is>
-          <t>SRC_SK_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X336" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis, congenital</t>
-        </is>
-      </c>
-      <c r="Y336" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z336" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
@@ -61576,64 +61554,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB336" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC336" t="inlineStr">
-        <is>
-          <t>country:SK:national</t>
-        </is>
-      </c>
-      <c r="AD336" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE336" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF336" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG336" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH336" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI336" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ336" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK336" t="inlineStr">
-        <is>
-          <t>Slovakia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM336" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN336" t="b">
-        <v>1</v>
-      </c>
       <c r="AO336" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -61651,7 +61571,7 @@
       </c>
       <c r="AS336" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT336" t="n">
@@ -61669,7 +61589,7 @@
       </c>
       <c r="AW336" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="AX336" t="inlineStr">
@@ -61689,7 +61609,7 @@
       </c>
       <c r="BA336" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="BB336" t="inlineStr">
@@ -61726,17 +61646,17 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -61770,84 +61690,170 @@
         </is>
       </c>
       <c r="N337" t="n">
+        <v>0</v>
+      </c>
+      <c r="O337" t="n">
+        <v>0</v>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W337" t="inlineStr">
+        <is>
+          <t>SRC_HR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X337" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z337" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB337" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC337" t="inlineStr">
+        <is>
+          <t>country:HR:national</t>
+        </is>
+      </c>
+      <c r="AD337" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE337" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF337" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG337" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH337" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI337" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ337" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK337" t="inlineStr">
+        <is>
+          <t>Croatia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM337" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN337" t="b">
         <v>1</v>
       </c>
-      <c r="O337" t="n">
+      <c r="AO337" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP337" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ337" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS337" t="inlineStr">
+        <is>
+          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT337" t="n">
         <v>1</v>
       </c>
-      <c r="Q337" t="n">
-        <v>0</v>
-      </c>
-      <c r="R337" t="n">
-        <v>0.004326608212170636</v>
-      </c>
-      <c r="S337" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO337" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP337" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR337" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS337" t="inlineStr"/>
-      <c r="AT337" t="n">
-        <v>0</v>
-      </c>
       <c r="AU337" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV337" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW337" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="AX337" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY337" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ337" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA337" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="BB337" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC337" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -61879,12 +61885,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -61909,93 +61915,104 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N338" t="n">
-        <v>578</v>
+        <v>2</v>
       </c>
       <c r="O338" t="n">
-        <v>578</v>
-      </c>
-      <c r="Q338" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R338" t="n">
-        <v>0.2716007086147069</v>
+        <v>0.02076350092143226</v>
       </c>
       <c r="S338" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO338" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP338" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR338" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS338" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ338" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS338" t="inlineStr">
+        <is>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU338" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV338" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW338" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX338" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY338" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ338" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA338" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB338" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC338" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -62022,17 +62039,17 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -62057,93 +62074,179 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N339" t="n">
-        <v>590</v>
+        <v>2</v>
       </c>
       <c r="O339" t="n">
-        <v>590</v>
-      </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
-      <c r="R339" t="n">
-        <v>0.2772394776516905</v>
-      </c>
-      <c r="S339" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W339" t="inlineStr">
+        <is>
+          <t>SRC_HU_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X339" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z339" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB339" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC339" t="inlineStr">
+        <is>
+          <t>country:HU:national</t>
+        </is>
+      </c>
+      <c r="AD339" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE339" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF339" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG339" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH339" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI339" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ339" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK339" t="inlineStr">
+        <is>
+          <t>Hungary annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM339" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN339" t="b">
+        <v>1</v>
       </c>
       <c r="AO339" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP339" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR339" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS339" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ339" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS339" t="inlineStr">
+        <is>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU339" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV339" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW339" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX339" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY339" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ339" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA339" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB339" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC339" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -62170,17 +62273,17 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -62205,93 +62308,184 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N340" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O340" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q340" t="n">
         <v>0</v>
       </c>
-      <c r="R340" t="n">
-        <v>0.008653216424341272</v>
-      </c>
-      <c r="S340" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>SER_IS_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W340" t="inlineStr">
+        <is>
+          <t>SRC_IS_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X340" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y340" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z340" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB340" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC340" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD340" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE340" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF340" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG340" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH340" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI340" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ340" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK340" t="inlineStr">
+        <is>
+          <t>Iceland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM340" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN340" t="b">
+        <v>0</v>
       </c>
       <c r="AO340" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP340" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ340" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR340" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS340" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS340" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT340" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU340" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV340" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW340" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX340" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY340" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ340" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA340" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB340" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC340" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -62323,12 +62517,12 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -62353,93 +62547,104 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N341" t="n">
-        <v>652</v>
+        <v>2</v>
       </c>
       <c r="O341" t="n">
-        <v>652</v>
-      </c>
-      <c r="Q341" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R341" t="n">
-        <v>0.3063731176761054</v>
+        <v>0.0706677697905531</v>
       </c>
       <c r="S341" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO341" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP341" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR341" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS341" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ341" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS341" t="inlineStr">
+        <is>
+          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU341" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV341" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW341" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="AX341" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY341" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ341" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA341" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="BB341" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC341" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -62466,17 +62671,17 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -62501,93 +62706,179 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N342" t="n">
+        <v>2</v>
+      </c>
+      <c r="O342" t="n">
+        <v>2</v>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W342" t="inlineStr">
+        <is>
+          <t>SRC_LT_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X342" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y342" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z342" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA342" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB342" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC342" t="inlineStr">
+        <is>
+          <t>country:LT:national</t>
+        </is>
+      </c>
+      <c r="AD342" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE342" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF342" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG342" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH342" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI342" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ342" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK342" t="inlineStr">
+        <is>
+          <t>Lithuania annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM342" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN342" t="b">
         <v>1</v>
       </c>
-      <c r="O342" t="n">
+      <c r="AO342" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP342" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ342" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS342" t="inlineStr">
+        <is>
+          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT342" t="n">
         <v>1</v>
       </c>
-      <c r="Q342" t="n">
-        <v>0</v>
-      </c>
-      <c r="R342" t="n">
-        <v>0.004326608212170636</v>
-      </c>
-      <c r="S342" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO342" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP342" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR342" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS342" t="inlineStr"/>
-      <c r="AT342" t="n">
-        <v>0</v>
-      </c>
       <c r="AU342" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV342" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW342" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="AX342" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY342" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ342" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA342" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="BB342" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC342" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -62619,12 +62910,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -62649,93 +62940,104 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N343" t="n">
-        <v>588</v>
+        <v>0</v>
       </c>
       <c r="O343" t="n">
-        <v>588</v>
-      </c>
-      <c r="Q343" t="n">
         <v>0</v>
       </c>
       <c r="R343" t="n">
-        <v>0.2762996828121932</v>
+        <v>0</v>
       </c>
       <c r="S343" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO343" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP343" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR343" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS343" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ343" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS343" t="inlineStr">
+        <is>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU343" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV343" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW343" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX343" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY343" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ343" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA343" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB343" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC343" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -62762,17 +63064,17 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -62797,93 +63099,179 @@
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N344" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O344" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q344" t="n">
         <v>0</v>
       </c>
-      <c r="R344" t="n">
-        <v>0.008653216424341272</v>
-      </c>
-      <c r="S344" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W344" t="inlineStr">
+        <is>
+          <t>SRC_LU_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X344" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y344" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z344" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB344" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC344" t="inlineStr">
+        <is>
+          <t>country:LU:national</t>
+        </is>
+      </c>
+      <c r="AD344" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE344" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF344" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG344" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH344" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI344" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ344" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK344" t="inlineStr">
+        <is>
+          <t>Luxembourg annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM344" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN344" t="b">
+        <v>1</v>
       </c>
       <c r="AO344" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP344" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR344" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS344" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ344" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS344" t="inlineStr">
+        <is>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU344" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV344" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW344" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX344" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY344" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ344" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA344" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB344" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC344" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -62915,12 +63303,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -62945,93 +63333,104 @@
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N345" t="n">
-        <v>586</v>
+        <v>0</v>
       </c>
       <c r="O345" t="n">
-        <v>586</v>
-      </c>
-      <c r="Q345" t="n">
         <v>0</v>
       </c>
       <c r="R345" t="n">
-        <v>0.2753598879726959</v>
+        <v>0</v>
       </c>
       <c r="S345" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO345" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP345" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR345" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS345" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ345" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS345" t="inlineStr">
+        <is>
+          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU345" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV345" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW345" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX345" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY345" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ345" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA345" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB345" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC345" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -63058,17 +63457,17 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -63093,93 +63492,179 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N346" t="n">
+        <v>0</v>
+      </c>
+      <c r="O346" t="n">
+        <v>0</v>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W346" t="inlineStr">
+        <is>
+          <t>SRC_LV_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X346" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y346" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z346" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB346" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC346" t="inlineStr">
+        <is>
+          <t>country:LV:national</t>
+        </is>
+      </c>
+      <c r="AD346" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE346" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF346" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG346" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH346" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI346" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ346" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK346" t="inlineStr">
+        <is>
+          <t>Latvia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM346" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN346" t="b">
         <v>1</v>
       </c>
-      <c r="O346" t="n">
+      <c r="AO346" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP346" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ346" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS346" t="inlineStr">
+        <is>
+          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT346" t="n">
         <v>1</v>
       </c>
-      <c r="Q346" t="n">
-        <v>0</v>
-      </c>
-      <c r="R346" t="n">
-        <v>0.004326608212170636</v>
-      </c>
-      <c r="S346" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO346" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP346" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR346" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS346" t="inlineStr"/>
-      <c r="AT346" t="n">
-        <v>0</v>
-      </c>
       <c r="AU346" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV346" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW346" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX346" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY346" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ346" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA346" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB346" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC346" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -63211,12 +63696,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -63241,93 +63726,104 @@
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N347" t="n">
-        <v>635</v>
+        <v>0</v>
       </c>
       <c r="O347" t="n">
-        <v>635</v>
-      </c>
-      <c r="Q347" t="n">
         <v>0</v>
       </c>
       <c r="R347" t="n">
-        <v>0.2983848615403787</v>
+        <v>0</v>
       </c>
       <c r="S347" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA347" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO347" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP347" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR347" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS347" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ347" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS347" t="inlineStr">
+        <is>
+          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT347" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU347" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV347" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW347" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX347" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY347" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ347" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA347" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB347" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC347" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -63354,17 +63850,17 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -63389,93 +63885,179 @@
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N348" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O348" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q348" t="n">
         <v>0</v>
       </c>
-      <c r="R348" t="n">
-        <v>0.01297982463651191</v>
-      </c>
-      <c r="S348" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W348" t="inlineStr">
+        <is>
+          <t>SRC_MT_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X348" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y348" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z348" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA348" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB348" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC348" t="inlineStr">
+        <is>
+          <t>country:MT:national</t>
+        </is>
+      </c>
+      <c r="AD348" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE348" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF348" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG348" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH348" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI348" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ348" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK348" t="inlineStr">
+        <is>
+          <t>Malta annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM348" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN348" t="b">
+        <v>1</v>
       </c>
       <c r="AO348" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP348" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR348" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS348" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ348" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS348" t="inlineStr">
+        <is>
+          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU348" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV348" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW348" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX348" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY348" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ348" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA348" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB348" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC348" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -63507,12 +64089,12 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -63537,93 +64119,104 @@
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N349" t="n">
-        <v>646</v>
+        <v>15</v>
       </c>
       <c r="O349" t="n">
-        <v>646</v>
-      </c>
-      <c r="Q349" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R349" t="n">
-        <v>0.3035537331576136</v>
+        <v>0.03932785084739523</v>
       </c>
       <c r="S349" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA349" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO349" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP349" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR349" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS349" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ349" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS349" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU349" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV349" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW349" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX349" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY349" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ349" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA349" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB349" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC349" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -63650,17 +64243,17 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -63685,93 +64278,179 @@
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N350" t="n">
+        <v>15</v>
+      </c>
+      <c r="O350" t="n">
+        <v>15</v>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W350" t="inlineStr">
+        <is>
+          <t>SRC_PL_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X350" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y350" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z350" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB350" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC350" t="inlineStr">
+        <is>
+          <t>country:PL:national</t>
+        </is>
+      </c>
+      <c r="AD350" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE350" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF350" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG350" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH350" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI350" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ350" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK350" t="inlineStr">
+        <is>
+          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM350" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN350" t="b">
         <v>1</v>
       </c>
-      <c r="O350" t="n">
+      <c r="AO350" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP350" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ350" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS350" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT350" t="n">
         <v>1</v>
       </c>
-      <c r="Q350" t="n">
-        <v>0</v>
-      </c>
-      <c r="R350" t="n">
-        <v>0.004326608212170636</v>
-      </c>
-      <c r="S350" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO350" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP350" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR350" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS350" t="inlineStr"/>
-      <c r="AT350" t="n">
-        <v>0</v>
-      </c>
       <c r="AU350" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV350" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW350" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX350" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY350" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ350" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA350" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB350" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC350" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -63803,12 +64482,12 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -63833,93 +64512,104 @@
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N351" t="n">
-        <v>678</v>
+        <v>1</v>
       </c>
       <c r="O351" t="n">
-        <v>678</v>
-      </c>
-      <c r="Q351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R351" t="n">
-        <v>0.3185904505895697</v>
+        <v>0.009604456314058422</v>
       </c>
       <c r="S351" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO351" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP351" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR351" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS351" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ351" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS351" t="inlineStr">
+        <is>
+          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU351" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV351" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW351" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="AX351" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY351" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ351" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA351" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="BB351" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC351" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -63946,17 +64636,17 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -63981,12 +64671,12 @@
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N352" t="n">
@@ -63995,79 +64685,165 @@
       <c r="O352" t="n">
         <v>1</v>
       </c>
-      <c r="Q352" t="n">
-        <v>0</v>
-      </c>
-      <c r="R352" t="n">
-        <v>0.004326608212170636</v>
-      </c>
-      <c r="S352" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W352" t="inlineStr">
+        <is>
+          <t>SRC_PT_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X352" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y352" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z352" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB352" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC352" t="inlineStr">
+        <is>
+          <t>country:PT:national</t>
+        </is>
+      </c>
+      <c r="AD352" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE352" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF352" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG352" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH352" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI352" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ352" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK352" t="inlineStr">
+        <is>
+          <t>Portugal annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM352" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN352" t="b">
+        <v>1</v>
       </c>
       <c r="AO352" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP352" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR352" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS352" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ352" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS352" t="inlineStr">
+        <is>
+          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU352" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV352" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW352" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="AX352" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY352" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ352" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA352" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="BB352" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC352" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -64099,12 +64875,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -64129,93 +64905,104 @@
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N353" t="n">
-        <v>695</v>
+        <v>0</v>
       </c>
       <c r="O353" t="n">
-        <v>695</v>
-      </c>
-      <c r="Q353" t="n">
         <v>0</v>
       </c>
       <c r="R353" t="n">
-        <v>0.3265787067252964</v>
+        <v>0</v>
       </c>
       <c r="S353" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO353" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP353" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR353" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS353" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ353" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS353" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU353" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV353" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW353" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="AX353" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY353" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ353" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA353" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="BB353" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC353" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -64242,17 +65029,17 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -64277,93 +65064,179 @@
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N354" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O354" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q354" t="n">
         <v>0</v>
       </c>
-      <c r="R354" t="n">
-        <v>0.01297982463651191</v>
-      </c>
-      <c r="S354" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W354" t="inlineStr">
+        <is>
+          <t>SRC_RO_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X354" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y354" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z354" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB354" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC354" t="inlineStr">
+        <is>
+          <t>country:RO:national</t>
+        </is>
+      </c>
+      <c r="AD354" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE354" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF354" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG354" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH354" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI354" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ354" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK354" t="inlineStr">
+        <is>
+          <t>Romania annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM354" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN354" t="b">
+        <v>1</v>
       </c>
       <c r="AO354" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP354" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR354" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS354" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ354" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS354" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU354" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV354" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW354" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="AX354" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY354" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ354" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA354" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="BB354" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC354" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -64395,12 +65268,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -64425,93 +65298,104 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N355" t="n">
-        <v>565</v>
+        <v>3</v>
       </c>
       <c r="O355" t="n">
-        <v>565</v>
-      </c>
-      <c r="Q355" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R355" t="n">
-        <v>0.2654920421579747</v>
+        <v>0.1417051474867175</v>
       </c>
       <c r="S355" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO355" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP355" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR355" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS355" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ355" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS355" t="inlineStr">
+        <is>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU355" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV355" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW355" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX355" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY355" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ355" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA355" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB355" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC355" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -64538,17 +65422,17 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -64573,93 +65457,179 @@
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N356" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O356" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q356" t="n">
-        <v>0</v>
-      </c>
-      <c r="R356" t="n">
-        <v>0.008653216424341272</v>
-      </c>
-      <c r="S356" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W356" t="inlineStr">
+        <is>
+          <t>SRC_SI_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X356" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y356" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z356" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB356" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC356" t="inlineStr">
+        <is>
+          <t>country:SI:national</t>
+        </is>
+      </c>
+      <c r="AD356" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE356" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF356" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG356" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH356" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI356" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ356" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK356" t="inlineStr">
+        <is>
+          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM356" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN356" t="b">
+        <v>1</v>
       </c>
       <c r="AO356" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP356" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR356" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS356" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ356" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS356" t="inlineStr">
+        <is>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU356" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV356" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW356" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX356" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY356" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ356" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA356" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB356" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC356" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -64691,12 +65661,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -64721,93 +65691,104 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N357" t="n">
-        <v>464</v>
+        <v>2</v>
       </c>
       <c r="O357" t="n">
-        <v>464</v>
-      </c>
-      <c r="Q357" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R357" t="n">
-        <v>0.2180324027633633</v>
+        <v>0.03653047436099524</v>
       </c>
       <c r="S357" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO357" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP357" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR357" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS357" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ357" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS357" t="inlineStr">
+        <is>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU357" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV357" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW357" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="AX357" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY357" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ357" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA357" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="BB357" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC357" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -64834,126 +65815,3468 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N358" t="n">
+        <v>2</v>
+      </c>
+      <c r="O358" t="n">
+        <v>2</v>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W358" t="inlineStr">
+        <is>
+          <t>SRC_SK_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X358" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y358" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z358" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB358" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC358" t="inlineStr">
+        <is>
+          <t>country:SK:national</t>
+        </is>
+      </c>
+      <c r="AD358" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE358" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF358" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG358" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH358" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI358" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ358" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK358" t="inlineStr">
+        <is>
+          <t>Slovakia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM358" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN358" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO358" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP358" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ358" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS358" t="inlineStr">
+        <is>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT358" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU358" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV358" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW358" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX358" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY358" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA358" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB358" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC358" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F358" t="inlineStr">
+      <c r="F359" t="inlineStr">
         <is>
           <t>TW</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr">
+      <c r="G359" t="inlineStr">
         <is>
           <t>Taiwan, China</t>
         </is>
       </c>
-      <c r="H358" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="I358" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="J358" t="inlineStr">
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
         <is>
           <t>弓形体病</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr">
+      <c r="K359" t="inlineStr">
         <is>
           <t>Parasitic</t>
         </is>
       </c>
-      <c r="L358" t="inlineStr">
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N359" t="n">
+        <v>1</v>
+      </c>
+      <c r="O359" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>0</v>
+      </c>
+      <c r="R359" t="n">
+        <v>0.004326608212170636</v>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO359" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP359" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR359" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS359" t="inlineStr"/>
+      <c r="AT359" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU359" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV359" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW359" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX359" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY359" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA359" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB359" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC359" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="N360" t="n">
+        <v>578</v>
+      </c>
+      <c r="O360" t="n">
+        <v>578</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>0</v>
+      </c>
+      <c r="R360" t="n">
+        <v>0.2716007086147069</v>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO360" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP360" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR360" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS360" t="inlineStr"/>
+      <c r="AT360" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU360" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV360" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW360" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX360" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY360" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA360" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB360" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC360" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="N361" t="n">
+        <v>590</v>
+      </c>
+      <c r="O361" t="n">
+        <v>590</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>0</v>
+      </c>
+      <c r="R361" t="n">
+        <v>0.2772394776516905</v>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO361" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP361" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR361" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS361" t="inlineStr"/>
+      <c r="AT361" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU361" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV361" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW361" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX361" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY361" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA361" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB361" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC361" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="N362" t="n">
+        <v>2</v>
+      </c>
+      <c r="O362" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>0</v>
+      </c>
+      <c r="R362" t="n">
+        <v>0.008653216424341272</v>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO362" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP362" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR362" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS362" t="inlineStr"/>
+      <c r="AT362" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU362" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV362" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW362" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX362" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY362" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA362" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB362" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC362" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="N363" t="n">
+        <v>652</v>
+      </c>
+      <c r="O363" t="n">
+        <v>652</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>0</v>
+      </c>
+      <c r="R363" t="n">
+        <v>0.3063731176761054</v>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO363" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP363" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR363" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS363" t="inlineStr"/>
+      <c r="AT363" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU363" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV363" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW363" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX363" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY363" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA363" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB363" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC363" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="N364" t="n">
+        <v>1</v>
+      </c>
+      <c r="O364" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>0</v>
+      </c>
+      <c r="R364" t="n">
+        <v>0.004326608212170636</v>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO364" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP364" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR364" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS364" t="inlineStr"/>
+      <c r="AT364" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU364" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV364" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW364" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX364" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY364" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA364" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB364" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC364" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="N365" t="n">
+        <v>588</v>
+      </c>
+      <c r="O365" t="n">
+        <v>588</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>0</v>
+      </c>
+      <c r="R365" t="n">
+        <v>0.2762996828121932</v>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO365" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP365" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR365" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS365" t="inlineStr"/>
+      <c r="AT365" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU365" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV365" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW365" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX365" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY365" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA365" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB365" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC365" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="N366" t="n">
+        <v>2</v>
+      </c>
+      <c r="O366" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q366" t="n">
+        <v>0</v>
+      </c>
+      <c r="R366" t="n">
+        <v>0.008653216424341272</v>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO366" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP366" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR366" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS366" t="inlineStr"/>
+      <c r="AT366" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU366" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV366" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW366" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX366" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY366" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ366" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA366" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB366" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC366" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="N367" t="n">
+        <v>586</v>
+      </c>
+      <c r="O367" t="n">
+        <v>586</v>
+      </c>
+      <c r="Q367" t="n">
+        <v>0</v>
+      </c>
+      <c r="R367" t="n">
+        <v>0.2753598879726959</v>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO367" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP367" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR367" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS367" t="inlineStr"/>
+      <c r="AT367" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU367" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV367" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW367" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX367" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY367" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA367" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB367" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC367" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="N368" t="n">
+        <v>1</v>
+      </c>
+      <c r="O368" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q368" t="n">
+        <v>0</v>
+      </c>
+      <c r="R368" t="n">
+        <v>0.004326608212170636</v>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO368" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP368" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR368" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS368" t="inlineStr"/>
+      <c r="AT368" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU368" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV368" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW368" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX368" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY368" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ368" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA368" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB368" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC368" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="N369" t="n">
+        <v>635</v>
+      </c>
+      <c r="O369" t="n">
+        <v>635</v>
+      </c>
+      <c r="Q369" t="n">
+        <v>0</v>
+      </c>
+      <c r="R369" t="n">
+        <v>0.2983848615403787</v>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO369" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP369" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR369" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS369" t="inlineStr"/>
+      <c r="AT369" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU369" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV369" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW369" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX369" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY369" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA369" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB369" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC369" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="N370" t="n">
+        <v>3</v>
+      </c>
+      <c r="O370" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q370" t="n">
+        <v>0</v>
+      </c>
+      <c r="R370" t="n">
+        <v>0.01297982463651191</v>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO370" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP370" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR370" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS370" t="inlineStr"/>
+      <c r="AT370" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU370" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV370" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW370" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX370" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY370" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ370" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA370" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB370" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC370" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="N371" t="n">
+        <v>646</v>
+      </c>
+      <c r="O371" t="n">
+        <v>646</v>
+      </c>
+      <c r="Q371" t="n">
+        <v>0</v>
+      </c>
+      <c r="R371" t="n">
+        <v>0.3035537331576136</v>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO371" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP371" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR371" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS371" t="inlineStr"/>
+      <c r="AT371" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU371" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV371" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW371" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX371" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY371" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ371" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA371" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB371" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC371" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="N372" t="n">
+        <v>1</v>
+      </c>
+      <c r="O372" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q372" t="n">
+        <v>0</v>
+      </c>
+      <c r="R372" t="n">
+        <v>0.004326608212170636</v>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO372" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP372" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR372" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS372" t="inlineStr"/>
+      <c r="AT372" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU372" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV372" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW372" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX372" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY372" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ372" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA372" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB372" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC372" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="N373" t="n">
+        <v>678</v>
+      </c>
+      <c r="O373" t="n">
+        <v>678</v>
+      </c>
+      <c r="Q373" t="n">
+        <v>0</v>
+      </c>
+      <c r="R373" t="n">
+        <v>0.3185904505895697</v>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO373" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP373" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR373" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS373" t="inlineStr"/>
+      <c r="AT373" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU373" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV373" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW373" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX373" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY373" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ373" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA373" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB373" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC373" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="N374" t="n">
+        <v>1</v>
+      </c>
+      <c r="O374" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q374" t="n">
+        <v>0</v>
+      </c>
+      <c r="R374" t="n">
+        <v>0.004326608212170636</v>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO374" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP374" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR374" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS374" t="inlineStr"/>
+      <c r="AT374" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU374" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV374" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW374" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX374" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY374" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ374" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA374" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB374" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC374" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="N375" t="n">
+        <v>695</v>
+      </c>
+      <c r="O375" t="n">
+        <v>695</v>
+      </c>
+      <c r="Q375" t="n">
+        <v>0</v>
+      </c>
+      <c r="R375" t="n">
+        <v>0.3265787067252964</v>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO375" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP375" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR375" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS375" t="inlineStr"/>
+      <c r="AT375" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU375" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV375" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW375" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX375" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY375" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ375" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA375" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB375" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC375" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="N376" t="n">
+        <v>3</v>
+      </c>
+      <c r="O376" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q376" t="n">
+        <v>0</v>
+      </c>
+      <c r="R376" t="n">
+        <v>0.01297982463651191</v>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO376" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP376" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR376" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS376" t="inlineStr"/>
+      <c r="AT376" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU376" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV376" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW376" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX376" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY376" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ376" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA376" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB376" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC376" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="N377" t="n">
+        <v>565</v>
+      </c>
+      <c r="O377" t="n">
+        <v>565</v>
+      </c>
+      <c r="Q377" t="n">
+        <v>0</v>
+      </c>
+      <c r="R377" t="n">
+        <v>0.2654920421579747</v>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO377" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP377" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR377" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS377" t="inlineStr"/>
+      <c r="AT377" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU377" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV377" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW377" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX377" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY377" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ377" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA377" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB377" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC377" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="N378" t="n">
+        <v>2</v>
+      </c>
+      <c r="O378" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q378" t="n">
+        <v>0</v>
+      </c>
+      <c r="R378" t="n">
+        <v>0.008653216424341272</v>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO378" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP378" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR378" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS378" t="inlineStr"/>
+      <c r="AT378" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU378" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV378" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW378" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX378" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY378" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ378" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA378" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB378" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC378" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
         <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="M358" t="inlineStr">
+      <c r="M379" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="N358" t="n">
+      <c r="N379" t="n">
+        <v>464</v>
+      </c>
+      <c r="O379" t="n">
+        <v>464</v>
+      </c>
+      <c r="Q379" t="n">
+        <v>0</v>
+      </c>
+      <c r="R379" t="n">
+        <v>0.2180324027633633</v>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO379" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP379" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR379" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS379" t="inlineStr"/>
+      <c r="AT379" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU379" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV379" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW379" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX379" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY379" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ379" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA379" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB379" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC379" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="N380" t="n">
         <v>3</v>
       </c>
-      <c r="O358" t="n">
+      <c r="O380" t="n">
         <v>3</v>
       </c>
-      <c r="Q358" t="n">
+      <c r="Q380" t="n">
         <v>0</v>
       </c>
-      <c r="R358" t="n">
+      <c r="R380" t="n">
         <v>0.01297982463651191</v>
       </c>
-      <c r="S358" t="inlineStr">
+      <c r="S380" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO358" t="inlineStr">
+      <c r="AO380" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP358" t="inlineStr">
+      <c r="AP380" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR358" t="inlineStr">
+      <c r="AR380" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS358" t="inlineStr"/>
-      <c r="AT358" t="n">
+      <c r="AS380" t="inlineStr"/>
+      <c r="AT380" t="n">
         <v>0</v>
       </c>
-      <c r="AU358" t="inlineStr">
+      <c r="AU380" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV358" t="inlineStr">
+      <c r="AV380" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="AW358" t="inlineStr">
+      <c r="AW380" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="AX358" t="inlineStr">
+      <c r="AX380" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="AY358" t="inlineStr">
+      <c r="AY380" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="AZ358" t="inlineStr">
+      <c r="AZ380" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="BA358" t="inlineStr">
+      <c r="BA380" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="BB358" t="inlineStr">
+      <c r="BB380" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="BC358" t="inlineStr">
+      <c r="BC380" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -65075,7 +69398,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>239</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -65085,7 +69408,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>357</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11">
@@ -65105,7 +69428,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>118</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -65137,7 +69460,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33709</v>
+        <v>33729</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d085/2020-2025.xlsx
+++ b/diseases/d085/2020-2025.xlsx
@@ -60313,12 +60313,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -60352,13 +60352,13 @@
         </is>
       </c>
       <c r="N330" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O330" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R330" t="n">
-        <v>0</v>
+        <v>0.002378826319089375</v>
       </c>
       <c r="S330" t="inlineStr">
         <is>
@@ -60367,7 +60367,7 @@
       </c>
       <c r="U330" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
+          <t>SER_DE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
@@ -60392,7 +60392,7 @@
       </c>
       <c r="AS330" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
+          <t>SER_DE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT330" t="n">
@@ -60405,42 +60405,42 @@
       </c>
       <c r="AV330" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW330" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY330" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ330" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA330" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB330" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC330" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -60472,12 +60472,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -60511,24 +60511,24 @@
         </is>
       </c>
       <c r="N331" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O331" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U331" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
+          <t>SER_DE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V331" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
+          <t>SER_DE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W331" t="inlineStr">
         <is>
-          <t>SRC_EE_ECDC_ATLAS</t>
+          <t>SRC_DE_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X331" t="inlineStr">
@@ -60558,7 +60558,7 @@
       </c>
       <c r="AC331" t="inlineStr">
         <is>
-          <t>country:EE:national</t>
+          <t>country:DE:national</t>
         </is>
       </c>
       <c r="AD331" t="inlineStr">
@@ -60598,7 +60598,7 @@
       </c>
       <c r="AK331" t="inlineStr">
         <is>
-          <t>Estonia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM331" t="inlineStr">
@@ -60626,7 +60626,7 @@
       </c>
       <c r="AS331" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
+          <t>SER_DE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT331" t="n">
@@ -60639,42 +60639,42 @@
       </c>
       <c r="AV331" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW331" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX331" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY331" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ331" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA331" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB331" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC331" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -60706,12 +60706,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -60745,13 +60745,13 @@
         </is>
       </c>
       <c r="N332" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O332" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R332" t="n">
-        <v>0.01879308392794999</v>
+        <v>0</v>
       </c>
       <c r="S332" t="inlineStr">
         <is>
@@ -60760,7 +60760,7 @@
       </c>
       <c r="U332" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
+          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -60785,7 +60785,7 @@
       </c>
       <c r="AS332" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
+          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT332" t="n">
@@ -60803,7 +60803,7 @@
       </c>
       <c r="AW332" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="AX332" t="inlineStr">
@@ -60823,7 +60823,7 @@
       </c>
       <c r="BA332" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="BB332" t="inlineStr">
@@ -60865,12 +60865,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -60904,24 +60904,24 @@
         </is>
       </c>
       <c r="N333" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O333" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="U333" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
+          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V333" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
+          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W333" t="inlineStr">
         <is>
-          <t>SRC_ES_ECDC_ATLAS</t>
+          <t>SRC_EE_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X333" t="inlineStr">
@@ -60951,7 +60951,7 @@
       </c>
       <c r="AC333" t="inlineStr">
         <is>
-          <t>country:ES:national</t>
+          <t>country:EE:national</t>
         </is>
       </c>
       <c r="AD333" t="inlineStr">
@@ -60991,7 +60991,7 @@
       </c>
       <c r="AK333" t="inlineStr">
         <is>
-          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Estonia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM333" t="inlineStr">
@@ -61019,7 +61019,7 @@
       </c>
       <c r="AS333" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
+          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT333" t="n">
@@ -61037,7 +61037,7 @@
       </c>
       <c r="AW333" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="AX333" t="inlineStr">
@@ -61057,7 +61057,7 @@
       </c>
       <c r="BA333" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="BB333" t="inlineStr">
@@ -61099,12 +61099,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -61138,13 +61138,13 @@
         </is>
       </c>
       <c r="N334" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O334" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="R334" t="n">
-        <v>0.02012306360160882</v>
+        <v>0.01879308392794999</v>
       </c>
       <c r="S334" t="inlineStr">
         <is>
@@ -61153,7 +61153,7 @@
       </c>
       <c r="U334" t="inlineStr">
         <is>
-          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -61178,7 +61178,7 @@
       </c>
       <c r="AS334" t="inlineStr">
         <is>
-          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT334" t="n">
@@ -61196,7 +61196,7 @@
       </c>
       <c r="AW334" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX334" t="inlineStr">
@@ -61216,7 +61216,7 @@
       </c>
       <c r="BA334" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB334" t="inlineStr">
@@ -61258,12 +61258,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -61297,24 +61297,24 @@
         </is>
       </c>
       <c r="N335" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O335" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U335" t="inlineStr">
         <is>
-          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V335" t="inlineStr">
         <is>
-          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W335" t="inlineStr">
         <is>
-          <t>SRC_GR_ECDC_ATLAS</t>
+          <t>SRC_ES_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X335" t="inlineStr">
@@ -61344,7 +61344,7 @@
       </c>
       <c r="AC335" t="inlineStr">
         <is>
-          <t>country:GR:national</t>
+          <t>country:ES:national</t>
         </is>
       </c>
       <c r="AD335" t="inlineStr">
@@ -61384,7 +61384,7 @@
       </c>
       <c r="AK335" t="inlineStr">
         <is>
-          <t>Greece annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM335" t="inlineStr">
@@ -61412,7 +61412,7 @@
       </c>
       <c r="AS335" t="inlineStr">
         <is>
-          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT335" t="n">
@@ -61430,7 +61430,7 @@
       </c>
       <c r="AW335" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX335" t="inlineStr">
@@ -61450,7 +61450,7 @@
       </c>
       <c r="BA335" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB335" t="inlineStr">
@@ -61492,12 +61492,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -61546,7 +61546,7 @@
       </c>
       <c r="U336" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_FI_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
@@ -61571,7 +61571,7 @@
       </c>
       <c r="AS336" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_FI_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT336" t="n">
@@ -61584,42 +61584,42 @@
       </c>
       <c r="AV336" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW336" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX336" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY336" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ336" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA336" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB336" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC336" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -61651,12 +61651,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -61697,17 +61697,17 @@
       </c>
       <c r="U337" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_FI_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V337" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_FI_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W337" t="inlineStr">
         <is>
-          <t>SRC_HR_ECDC_ATLAS</t>
+          <t>SRC_FI_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X337" t="inlineStr">
@@ -61737,7 +61737,7 @@
       </c>
       <c r="AC337" t="inlineStr">
         <is>
-          <t>country:HR:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD337" t="inlineStr">
@@ -61777,7 +61777,7 @@
       </c>
       <c r="AK337" t="inlineStr">
         <is>
-          <t>Croatia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Finland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM337" t="inlineStr">
@@ -61805,7 +61805,7 @@
       </c>
       <c r="AS337" t="inlineStr">
         <is>
-          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_FI_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT337" t="n">
@@ -61818,42 +61818,42 @@
       </c>
       <c r="AV337" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW337" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX337" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY337" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ337" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA337" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB337" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC337" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -61885,12 +61885,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -61930,7 +61930,7 @@
         <v>2</v>
       </c>
       <c r="R338" t="n">
-        <v>0.02076350092143226</v>
+        <v>0.02012306360160882</v>
       </c>
       <c r="S338" t="inlineStr">
         <is>
@@ -61939,7 +61939,7 @@
       </c>
       <c r="U338" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -61964,7 +61964,7 @@
       </c>
       <c r="AS338" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT338" t="n">
@@ -61982,7 +61982,7 @@
       </c>
       <c r="AW338" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX338" t="inlineStr">
@@ -62002,7 +62002,7 @@
       </c>
       <c r="BA338" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB338" t="inlineStr">
@@ -62044,12 +62044,12 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -62090,17 +62090,17 @@
       </c>
       <c r="U339" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V339" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W339" t="inlineStr">
         <is>
-          <t>SRC_HU_ECDC_ATLAS</t>
+          <t>SRC_GR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X339" t="inlineStr">
@@ -62130,7 +62130,7 @@
       </c>
       <c r="AC339" t="inlineStr">
         <is>
-          <t>country:HU:national</t>
+          <t>country:GR:national</t>
         </is>
       </c>
       <c r="AD339" t="inlineStr">
@@ -62170,7 +62170,7 @@
       </c>
       <c r="AK339" t="inlineStr">
         <is>
-          <t>Hungary annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Greece annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM339" t="inlineStr">
@@ -62198,7 +62198,7 @@
       </c>
       <c r="AS339" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_GR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT339" t="n">
@@ -62216,7 +62216,7 @@
       </c>
       <c r="AW339" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX339" t="inlineStr">
@@ -62236,7 +62236,7 @@
       </c>
       <c r="BA339" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB339" t="inlineStr">
@@ -62273,17 +62273,17 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -62322,34 +62322,17 @@
       <c r="O340" t="n">
         <v>0</v>
       </c>
+      <c r="R340" t="n">
+        <v>0</v>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U340" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V340" t="inlineStr">
-        <is>
-          <t>SER_IS_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W340" t="inlineStr">
-        <is>
-          <t>SRC_IS_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X340" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis, congenital</t>
-        </is>
-      </c>
-      <c r="Y340" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z340" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -62357,64 +62340,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB340" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC340" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD340" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE340" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF340" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG340" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH340" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI340" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ340" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK340" t="inlineStr">
-        <is>
-          <t>Iceland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM340" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN340" t="b">
-        <v>0</v>
-      </c>
       <c r="AO340" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -62422,7 +62347,7 @@
       </c>
       <c r="AP340" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ340" t="inlineStr">
@@ -62430,62 +62355,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR340" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS340" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT340" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU340" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV340" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW340" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="AX340" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY340" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ340" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA340" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="BB340" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC340" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -62512,17 +62432,17 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -62556,22 +62476,39 @@
         </is>
       </c>
       <c r="N341" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O341" t="n">
-        <v>2</v>
-      </c>
-      <c r="R341" t="n">
-        <v>0.0706677697905531</v>
-      </c>
-      <c r="S341" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U341" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W341" t="inlineStr">
+        <is>
+          <t>SRC_HR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X341" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y341" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z341" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -62579,6 +62516,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB341" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC341" t="inlineStr">
+        <is>
+          <t>country:HR:national</t>
+        </is>
+      </c>
+      <c r="AD341" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE341" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF341" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG341" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH341" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI341" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ341" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK341" t="inlineStr">
+        <is>
+          <t>Croatia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM341" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN341" t="b">
+        <v>1</v>
+      </c>
       <c r="AO341" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -62596,7 +62591,7 @@
       </c>
       <c r="AS341" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_HR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT341" t="n">
@@ -62614,7 +62609,7 @@
       </c>
       <c r="AW341" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="AX341" t="inlineStr">
@@ -62634,7 +62629,7 @@
       </c>
       <c r="BA341" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Croatia Annual Baseline</t>
         </is>
       </c>
       <c r="BB341" t="inlineStr">
@@ -62671,17 +62666,17 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -62720,34 +62715,17 @@
       <c r="O342" t="n">
         <v>2</v>
       </c>
+      <c r="R342" t="n">
+        <v>0.02076350092143226</v>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U342" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V342" t="inlineStr">
-        <is>
-          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W342" t="inlineStr">
-        <is>
-          <t>SRC_LT_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X342" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis, congenital</t>
-        </is>
-      </c>
-      <c r="Y342" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z342" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
@@ -62755,64 +62733,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB342" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC342" t="inlineStr">
-        <is>
-          <t>country:LT:national</t>
-        </is>
-      </c>
-      <c r="AD342" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE342" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF342" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG342" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH342" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI342" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ342" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK342" t="inlineStr">
-        <is>
-          <t>Lithuania annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM342" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN342" t="b">
-        <v>1</v>
-      </c>
       <c r="AO342" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -62830,7 +62750,7 @@
       </c>
       <c r="AS342" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT342" t="n">
@@ -62848,7 +62768,7 @@
       </c>
       <c r="AW342" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX342" t="inlineStr">
@@ -62868,7 +62788,7 @@
       </c>
       <c r="BA342" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB342" t="inlineStr">
@@ -62905,17 +62825,17 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -62949,22 +62869,39 @@
         </is>
       </c>
       <c r="N343" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O343" t="n">
-        <v>0</v>
-      </c>
-      <c r="R343" t="n">
-        <v>0</v>
-      </c>
-      <c r="S343" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U343" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W343" t="inlineStr">
+        <is>
+          <t>SRC_HU_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X343" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y343" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z343" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -62972,6 +62909,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB343" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC343" t="inlineStr">
+        <is>
+          <t>country:HU:national</t>
+        </is>
+      </c>
+      <c r="AD343" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE343" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF343" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG343" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH343" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI343" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ343" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK343" t="inlineStr">
+        <is>
+          <t>Hungary annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM343" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN343" t="b">
+        <v>1</v>
+      </c>
       <c r="AO343" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -62989,7 +62984,7 @@
       </c>
       <c r="AS343" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT343" t="n">
@@ -63007,7 +63002,7 @@
       </c>
       <c r="AW343" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX343" t="inlineStr">
@@ -63027,7 +63022,7 @@
       </c>
       <c r="BA343" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB343" t="inlineStr">
@@ -63064,17 +63059,17 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -63113,34 +63108,17 @@
       <c r="O344" t="n">
         <v>0</v>
       </c>
+      <c r="R344" t="n">
+        <v>0</v>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U344" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V344" t="inlineStr">
-        <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W344" t="inlineStr">
-        <is>
-          <t>SRC_LU_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X344" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis, congenital</t>
-        </is>
-      </c>
-      <c r="Y344" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z344" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
@@ -63148,64 +63126,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB344" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC344" t="inlineStr">
-        <is>
-          <t>country:LU:national</t>
-        </is>
-      </c>
-      <c r="AD344" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE344" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF344" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG344" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH344" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI344" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ344" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK344" t="inlineStr">
-        <is>
-          <t>Luxembourg annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM344" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN344" t="b">
-        <v>1</v>
-      </c>
       <c r="AO344" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -63223,7 +63143,7 @@
       </c>
       <c r="AS344" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT344" t="n">
@@ -63236,42 +63156,42 @@
       </c>
       <c r="AV344" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="AW344" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="AX344" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="AY344" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
       <c r="AZ344" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="BA344" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="BB344" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="BC344" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
     </row>
@@ -63298,17 +63218,17 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -63347,17 +63267,34 @@
       <c r="O345" t="n">
         <v>0</v>
       </c>
-      <c r="R345" t="n">
-        <v>0</v>
-      </c>
-      <c r="S345" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U345" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
+          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W345" t="inlineStr">
+        <is>
+          <t>SRC_IE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X345" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y345" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z345" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA345" t="inlineStr">
@@ -63365,6 +63302,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB345" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC345" t="inlineStr">
+        <is>
+          <t>country:IE:national</t>
+        </is>
+      </c>
+      <c r="AD345" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE345" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF345" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG345" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH345" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI345" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ345" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK345" t="inlineStr">
+        <is>
+          <t>Ireland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM345" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN345" t="b">
+        <v>1</v>
+      </c>
       <c r="AO345" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -63382,7 +63377,7 @@
       </c>
       <c r="AS345" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
+          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT345" t="n">
@@ -63395,42 +63390,42 @@
       </c>
       <c r="AV345" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="AW345" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="AX345" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="AY345" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
       <c r="AZ345" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="BA345" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="BB345" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="BC345" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
     </row>
@@ -63462,12 +63457,12 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -63508,17 +63503,17 @@
       </c>
       <c r="U346" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
+          <t>SER_IS_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V346" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
+          <t>SER_IS_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W346" t="inlineStr">
         <is>
-          <t>SRC_LV_ECDC_ATLAS</t>
+          <t>SRC_IS_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X346" t="inlineStr">
@@ -63548,7 +63543,7 @@
       </c>
       <c r="AC346" t="inlineStr">
         <is>
-          <t>country:LV:national</t>
+          <t>country:IS:national</t>
         </is>
       </c>
       <c r="AD346" t="inlineStr">
@@ -63588,7 +63583,7 @@
       </c>
       <c r="AK346" t="inlineStr">
         <is>
-          <t>Latvia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Iceland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM346" t="inlineStr">
@@ -63597,7 +63592,7 @@
         </is>
       </c>
       <c r="AN346" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO346" t="inlineStr">
         <is>
@@ -63606,7 +63601,7 @@
       </c>
       <c r="AP346" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ346" t="inlineStr">
@@ -63614,57 +63609,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR346" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS346" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT346" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU346" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV346" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW346" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX346" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY346" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ346" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA346" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB346" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC346" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -63696,12 +63696,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -63735,13 +63735,13 @@
         </is>
       </c>
       <c r="N347" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O347" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R347" t="n">
-        <v>0</v>
+        <v>0.0706677697905531</v>
       </c>
       <c r="S347" t="inlineStr">
         <is>
@@ -63750,7 +63750,7 @@
       </c>
       <c r="U347" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA347" t="inlineStr">
@@ -63775,7 +63775,7 @@
       </c>
       <c r="AS347" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT347" t="n">
@@ -63793,7 +63793,7 @@
       </c>
       <c r="AW347" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="AX347" t="inlineStr">
@@ -63813,7 +63813,7 @@
       </c>
       <c r="BA347" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="BB347" t="inlineStr">
@@ -63855,12 +63855,12 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -63894,24 +63894,24 @@
         </is>
       </c>
       <c r="N348" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O348" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U348" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V348" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W348" t="inlineStr">
         <is>
-          <t>SRC_MT_ECDC_ATLAS</t>
+          <t>SRC_LT_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X348" t="inlineStr">
@@ -63941,7 +63941,7 @@
       </c>
       <c r="AC348" t="inlineStr">
         <is>
-          <t>country:MT:national</t>
+          <t>country:LT:national</t>
         </is>
       </c>
       <c r="AD348" t="inlineStr">
@@ -63981,7 +63981,7 @@
       </c>
       <c r="AK348" t="inlineStr">
         <is>
-          <t>Malta annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Lithuania annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM348" t="inlineStr">
@@ -64009,7 +64009,7 @@
       </c>
       <c r="AS348" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT348" t="n">
@@ -64027,7 +64027,7 @@
       </c>
       <c r="AW348" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="AX348" t="inlineStr">
@@ -64047,7 +64047,7 @@
       </c>
       <c r="BA348" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="BB348" t="inlineStr">
@@ -64089,12 +64089,12 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -64128,13 +64128,13 @@
         </is>
       </c>
       <c r="N349" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O349" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R349" t="n">
-        <v>0.03932785084739523</v>
+        <v>0</v>
       </c>
       <c r="S349" t="inlineStr">
         <is>
@@ -64143,7 +64143,7 @@
       </c>
       <c r="U349" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
@@ -64168,7 +64168,7 @@
       </c>
       <c r="AS349" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT349" t="n">
@@ -64186,7 +64186,7 @@
       </c>
       <c r="AW349" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX349" t="inlineStr">
@@ -64206,7 +64206,7 @@
       </c>
       <c r="BA349" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB349" t="inlineStr">
@@ -64248,12 +64248,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -64287,24 +64287,24 @@
         </is>
       </c>
       <c r="N350" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O350" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U350" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V350" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W350" t="inlineStr">
         <is>
-          <t>SRC_PL_ECDC_ATLAS</t>
+          <t>SRC_LU_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X350" t="inlineStr">
@@ -64334,7 +64334,7 @@
       </c>
       <c r="AC350" t="inlineStr">
         <is>
-          <t>country:PL:national</t>
+          <t>country:LU:national</t>
         </is>
       </c>
       <c r="AD350" t="inlineStr">
@@ -64374,7 +64374,7 @@
       </c>
       <c r="AK350" t="inlineStr">
         <is>
-          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Luxembourg annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM350" t="inlineStr">
@@ -64402,7 +64402,7 @@
       </c>
       <c r="AS350" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT350" t="n">
@@ -64420,7 +64420,7 @@
       </c>
       <c r="AW350" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX350" t="inlineStr">
@@ -64440,7 +64440,7 @@
       </c>
       <c r="BA350" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB350" t="inlineStr">
@@ -64482,12 +64482,12 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -64521,13 +64521,13 @@
         </is>
       </c>
       <c r="N351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R351" t="n">
-        <v>0.009604456314058422</v>
+        <v>0</v>
       </c>
       <c r="S351" t="inlineStr">
         <is>
@@ -64536,7 +64536,7 @@
       </c>
       <c r="U351" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA351" t="inlineStr">
@@ -64561,7 +64561,7 @@
       </c>
       <c r="AS351" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT351" t="n">
@@ -64579,7 +64579,7 @@
       </c>
       <c r="AW351" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX351" t="inlineStr">
@@ -64599,7 +64599,7 @@
       </c>
       <c r="BA351" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB351" t="inlineStr">
@@ -64641,12 +64641,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -64680,24 +64680,24 @@
         </is>
       </c>
       <c r="N352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U352" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V352" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W352" t="inlineStr">
         <is>
-          <t>SRC_PT_ECDC_ATLAS</t>
+          <t>SRC_LV_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X352" t="inlineStr">
@@ -64727,7 +64727,7 @@
       </c>
       <c r="AC352" t="inlineStr">
         <is>
-          <t>country:PT:national</t>
+          <t>country:LV:national</t>
         </is>
       </c>
       <c r="AD352" t="inlineStr">
@@ -64767,7 +64767,7 @@
       </c>
       <c r="AK352" t="inlineStr">
         <is>
-          <t>Portugal annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Latvia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM352" t="inlineStr">
@@ -64795,7 +64795,7 @@
       </c>
       <c r="AS352" t="inlineStr">
         <is>
-          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT352" t="n">
@@ -64813,7 +64813,7 @@
       </c>
       <c r="AW352" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX352" t="inlineStr">
@@ -64833,7 +64833,7 @@
       </c>
       <c r="BA352" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB352" t="inlineStr">
@@ -64875,12 +64875,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -64929,7 +64929,7 @@
       </c>
       <c r="U353" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
@@ -64954,7 +64954,7 @@
       </c>
       <c r="AS353" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT353" t="n">
@@ -64972,7 +64972,7 @@
       </c>
       <c r="AW353" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX353" t="inlineStr">
@@ -64992,7 +64992,7 @@
       </c>
       <c r="BA353" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB353" t="inlineStr">
@@ -65034,12 +65034,12 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -65080,17 +65080,17 @@
       </c>
       <c r="U354" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V354" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W354" t="inlineStr">
         <is>
-          <t>SRC_RO_ECDC_ATLAS</t>
+          <t>SRC_MT_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X354" t="inlineStr">
@@ -65120,7 +65120,7 @@
       </c>
       <c r="AC354" t="inlineStr">
         <is>
-          <t>country:RO:national</t>
+          <t>country:MT:national</t>
         </is>
       </c>
       <c r="AD354" t="inlineStr">
@@ -65160,7 +65160,7 @@
       </c>
       <c r="AK354" t="inlineStr">
         <is>
-          <t>Romania annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Malta annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM354" t="inlineStr">
@@ -65188,7 +65188,7 @@
       </c>
       <c r="AS354" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT354" t="n">
@@ -65206,7 +65206,7 @@
       </c>
       <c r="AW354" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX354" t="inlineStr">
@@ -65226,7 +65226,7 @@
       </c>
       <c r="BA354" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB354" t="inlineStr">
@@ -65268,12 +65268,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -65307,13 +65307,13 @@
         </is>
       </c>
       <c r="N355" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O355" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="R355" t="n">
-        <v>0.1417051474867175</v>
+        <v>0.03932785084739523</v>
       </c>
       <c r="S355" t="inlineStr">
         <is>
@@ -65322,7 +65322,7 @@
       </c>
       <c r="U355" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA355" t="inlineStr">
@@ -65347,7 +65347,7 @@
       </c>
       <c r="AS355" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT355" t="n">
@@ -65365,7 +65365,7 @@
       </c>
       <c r="AW355" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX355" t="inlineStr">
@@ -65385,7 +65385,7 @@
       </c>
       <c r="BA355" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB355" t="inlineStr">
@@ -65427,12 +65427,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -65466,24 +65466,24 @@
         </is>
       </c>
       <c r="N356" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O356" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="U356" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V356" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W356" t="inlineStr">
         <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
+          <t>SRC_PL_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X356" t="inlineStr">
@@ -65513,7 +65513,7 @@
       </c>
       <c r="AC356" t="inlineStr">
         <is>
-          <t>country:SI:national</t>
+          <t>country:PL:national</t>
         </is>
       </c>
       <c r="AD356" t="inlineStr">
@@ -65553,7 +65553,7 @@
       </c>
       <c r="AK356" t="inlineStr">
         <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM356" t="inlineStr">
@@ -65581,7 +65581,7 @@
       </c>
       <c r="AS356" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT356" t="n">
@@ -65599,7 +65599,7 @@
       </c>
       <c r="AW356" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX356" t="inlineStr">
@@ -65619,7 +65619,7 @@
       </c>
       <c r="BA356" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB356" t="inlineStr">
@@ -65661,12 +65661,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -65700,13 +65700,13 @@
         </is>
       </c>
       <c r="N357" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O357" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R357" t="n">
-        <v>0.03653047436099524</v>
+        <v>0.009604456314058422</v>
       </c>
       <c r="S357" t="inlineStr">
         <is>
@@ -65715,7 +65715,7 @@
       </c>
       <c r="U357" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
@@ -65740,7 +65740,7 @@
       </c>
       <c r="AS357" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT357" t="n">
@@ -65758,7 +65758,7 @@
       </c>
       <c r="AW357" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="AX357" t="inlineStr">
@@ -65778,7 +65778,7 @@
       </c>
       <c r="BA357" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="BB357" t="inlineStr">
@@ -65820,12 +65820,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -65859,24 +65859,24 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O358" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U358" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V358" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W358" t="inlineStr">
         <is>
-          <t>SRC_SK_ECDC_ATLAS</t>
+          <t>SRC_PT_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X358" t="inlineStr">
@@ -65906,7 +65906,7 @@
       </c>
       <c r="AC358" t="inlineStr">
         <is>
-          <t>country:SK:national</t>
+          <t>country:PT:national</t>
         </is>
       </c>
       <c r="AD358" t="inlineStr">
@@ -65946,7 +65946,7 @@
       </c>
       <c r="AK358" t="inlineStr">
         <is>
-          <t>Slovakia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Portugal annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM358" t="inlineStr">
@@ -65974,7 +65974,7 @@
       </c>
       <c r="AS358" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT358" t="n">
@@ -65992,7 +65992,7 @@
       </c>
       <c r="AW358" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="AX358" t="inlineStr">
@@ -66012,7 +66012,7 @@
       </c>
       <c r="BA358" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Portugal Annual Baseline</t>
         </is>
       </c>
       <c r="BB358" t="inlineStr">
@@ -66054,12 +66054,12 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -66093,84 +66093,95 @@
         </is>
       </c>
       <c r="N359" t="n">
+        <v>0</v>
+      </c>
+      <c r="O359" t="n">
+        <v>0</v>
+      </c>
+      <c r="R359" t="n">
+        <v>0</v>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO359" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP359" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ359" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS359" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT359" t="n">
         <v>1</v>
       </c>
-      <c r="O359" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q359" t="n">
-        <v>0</v>
-      </c>
-      <c r="R359" t="n">
-        <v>0.004326608212170636</v>
-      </c>
-      <c r="S359" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO359" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP359" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR359" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS359" t="inlineStr"/>
-      <c r="AT359" t="n">
-        <v>0</v>
-      </c>
       <c r="AU359" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV359" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW359" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="AX359" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY359" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ359" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA359" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="BB359" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC359" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -66197,17 +66208,17 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -66232,93 +66243,179 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N360" t="n">
-        <v>578</v>
+        <v>0</v>
       </c>
       <c r="O360" t="n">
-        <v>578</v>
-      </c>
-      <c r="Q360" t="n">
         <v>0</v>
       </c>
-      <c r="R360" t="n">
-        <v>0.2716007086147069</v>
-      </c>
-      <c r="S360" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W360" t="inlineStr">
+        <is>
+          <t>SRC_RO_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X360" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y360" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z360" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB360" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC360" t="inlineStr">
+        <is>
+          <t>country:RO:national</t>
+        </is>
+      </c>
+      <c r="AD360" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE360" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF360" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG360" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH360" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI360" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ360" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK360" t="inlineStr">
+        <is>
+          <t>Romania annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM360" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN360" t="b">
+        <v>1</v>
       </c>
       <c r="AO360" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP360" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR360" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS360" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ360" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS360" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU360" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV360" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW360" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="AX360" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY360" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ360" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA360" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="BB360" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC360" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -66350,12 +66447,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -66380,93 +66477,104 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N361" t="n">
-        <v>590</v>
+        <v>3</v>
       </c>
       <c r="O361" t="n">
-        <v>590</v>
-      </c>
-      <c r="Q361" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R361" t="n">
-        <v>0.2772394776516905</v>
+        <v>0.1417051474867175</v>
       </c>
       <c r="S361" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO361" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP361" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR361" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS361" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ361" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS361" t="inlineStr">
+        <is>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU361" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV361" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW361" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX361" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY361" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ361" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA361" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB361" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC361" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -66493,17 +66601,17 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -66528,93 +66636,179 @@
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N362" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O362" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
-      <c r="R362" t="n">
-        <v>0.008653216424341272</v>
-      </c>
-      <c r="S362" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W362" t="inlineStr">
+        <is>
+          <t>SRC_SI_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X362" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y362" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z362" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB362" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC362" t="inlineStr">
+        <is>
+          <t>country:SI:national</t>
+        </is>
+      </c>
+      <c r="AD362" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE362" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF362" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG362" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH362" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI362" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ362" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK362" t="inlineStr">
+        <is>
+          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM362" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN362" t="b">
+        <v>1</v>
       </c>
       <c r="AO362" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP362" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR362" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS362" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ362" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS362" t="inlineStr">
+        <is>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU362" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV362" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW362" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX362" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY362" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ362" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA362" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB362" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC362" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -66646,12 +66840,12 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -66676,93 +66870,104 @@
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N363" t="n">
-        <v>652</v>
+        <v>2</v>
       </c>
       <c r="O363" t="n">
-        <v>652</v>
-      </c>
-      <c r="Q363" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R363" t="n">
-        <v>0.3063731176761054</v>
+        <v>0.03653047436099524</v>
       </c>
       <c r="S363" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO363" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP363" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR363" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS363" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ363" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS363" t="inlineStr">
+        <is>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU363" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV363" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW363" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="AX363" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY363" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ363" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA363" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="BB363" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC363" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -66789,17 +66994,17 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -66824,93 +67029,179 @@
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N364" t="n">
+        <v>2</v>
+      </c>
+      <c r="O364" t="n">
+        <v>2</v>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W364" t="inlineStr">
+        <is>
+          <t>SRC_SK_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X364" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y364" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z364" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB364" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC364" t="inlineStr">
+        <is>
+          <t>country:SK:national</t>
+        </is>
+      </c>
+      <c r="AD364" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE364" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF364" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG364" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH364" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI364" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ364" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK364" t="inlineStr">
+        <is>
+          <t>Slovakia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM364" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN364" t="b">
         <v>1</v>
       </c>
-      <c r="O364" t="n">
+      <c r="AO364" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP364" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ364" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS364" t="inlineStr">
+        <is>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT364" t="n">
         <v>1</v>
       </c>
-      <c r="Q364" t="n">
-        <v>0</v>
-      </c>
-      <c r="R364" t="n">
-        <v>0.004326608212170636</v>
-      </c>
-      <c r="S364" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO364" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP364" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR364" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS364" t="inlineStr"/>
-      <c r="AT364" t="n">
-        <v>0</v>
-      </c>
       <c r="AU364" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV364" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW364" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="AX364" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY364" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ364" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA364" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="BB364" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC364" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -66942,12 +67233,12 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -66972,25 +67263,25 @@
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="N365" t="n">
-        <v>588</v>
+        <v>1</v>
       </c>
       <c r="O365" t="n">
-        <v>588</v>
+        <v>1</v>
       </c>
       <c r="Q365" t="n">
         <v>0</v>
       </c>
       <c r="R365" t="n">
-        <v>0.2762996828121932</v>
+        <v>0.004326608212170636</v>
       </c>
       <c r="S365" t="inlineStr">
         <is>
@@ -67023,42 +67314,42 @@
       </c>
       <c r="AV365" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW365" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX365" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY365" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ365" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA365" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB365" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC365" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -67090,12 +67381,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -67120,25 +67411,25 @@
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="N366" t="n">
-        <v>2</v>
+        <v>578</v>
       </c>
       <c r="O366" t="n">
-        <v>2</v>
+        <v>578</v>
       </c>
       <c r="Q366" t="n">
         <v>0</v>
       </c>
       <c r="R366" t="n">
-        <v>0.008653216424341272</v>
+        <v>0.2716007086147069</v>
       </c>
       <c r="S366" t="inlineStr">
         <is>
@@ -67171,42 +67462,42 @@
       </c>
       <c r="AV366" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW366" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX366" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY366" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ366" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA366" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB366" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC366" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -67268,25 +67559,25 @@
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="N367" t="n">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="O367" t="n">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="Q367" t="n">
         <v>0</v>
       </c>
       <c r="R367" t="n">
-        <v>0.2753598879726959</v>
+        <v>0.2772394776516905</v>
       </c>
       <c r="S367" t="inlineStr">
         <is>
@@ -67416,25 +67707,25 @@
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="N368" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O368" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q368" t="n">
         <v>0</v>
       </c>
       <c r="R368" t="n">
-        <v>0.004326608212170636</v>
+        <v>0.008653216424341272</v>
       </c>
       <c r="S368" t="inlineStr">
         <is>
@@ -67564,25 +67855,25 @@
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="N369" t="n">
-        <v>635</v>
+        <v>652</v>
       </c>
       <c r="O369" t="n">
-        <v>635</v>
+        <v>652</v>
       </c>
       <c r="Q369" t="n">
         <v>0</v>
       </c>
       <c r="R369" t="n">
-        <v>0.2983848615403787</v>
+        <v>0.3063731176761054</v>
       </c>
       <c r="S369" t="inlineStr">
         <is>
@@ -67712,25 +68003,25 @@
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="N370" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O370" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q370" t="n">
         <v>0</v>
       </c>
       <c r="R370" t="n">
-        <v>0.01297982463651191</v>
+        <v>0.004326608212170636</v>
       </c>
       <c r="S370" t="inlineStr">
         <is>
@@ -67860,25 +68151,25 @@
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="N371" t="n">
-        <v>646</v>
+        <v>588</v>
       </c>
       <c r="O371" t="n">
-        <v>646</v>
+        <v>588</v>
       </c>
       <c r="Q371" t="n">
         <v>0</v>
       </c>
       <c r="R371" t="n">
-        <v>0.3035537331576136</v>
+        <v>0.2762996828121932</v>
       </c>
       <c r="S371" t="inlineStr">
         <is>
@@ -68008,25 +68299,25 @@
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="N372" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O372" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q372" t="n">
         <v>0</v>
       </c>
       <c r="R372" t="n">
-        <v>0.004326608212170636</v>
+        <v>0.008653216424341272</v>
       </c>
       <c r="S372" t="inlineStr">
         <is>
@@ -68156,25 +68447,25 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="N373" t="n">
-        <v>678</v>
+        <v>586</v>
       </c>
       <c r="O373" t="n">
-        <v>678</v>
+        <v>586</v>
       </c>
       <c r="Q373" t="n">
         <v>0</v>
       </c>
       <c r="R373" t="n">
-        <v>0.3185904505895697</v>
+        <v>0.2753598879726959</v>
       </c>
       <c r="S373" t="inlineStr">
         <is>
@@ -68304,12 +68595,12 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="N374" t="n">
@@ -68452,25 +68743,25 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="N375" t="n">
-        <v>695</v>
+        <v>635</v>
       </c>
       <c r="O375" t="n">
-        <v>695</v>
+        <v>635</v>
       </c>
       <c r="Q375" t="n">
         <v>0</v>
       </c>
       <c r="R375" t="n">
-        <v>0.3265787067252964</v>
+        <v>0.2983848615403787</v>
       </c>
       <c r="S375" t="inlineStr">
         <is>
@@ -68600,12 +68891,12 @@
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="N376" t="n">
@@ -68748,25 +69039,25 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="N377" t="n">
-        <v>565</v>
+        <v>646</v>
       </c>
       <c r="O377" t="n">
-        <v>565</v>
+        <v>646</v>
       </c>
       <c r="Q377" t="n">
         <v>0</v>
       </c>
       <c r="R377" t="n">
-        <v>0.2654920421579747</v>
+        <v>0.3035537331576136</v>
       </c>
       <c r="S377" t="inlineStr">
         <is>
@@ -68896,25 +69187,25 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="N378" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O378" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q378" t="n">
         <v>0</v>
       </c>
       <c r="R378" t="n">
-        <v>0.008653216424341272</v>
+        <v>0.004326608212170636</v>
       </c>
       <c r="S378" t="inlineStr">
         <is>
@@ -69044,25 +69335,25 @@
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="N379" t="n">
-        <v>464</v>
+        <v>678</v>
       </c>
       <c r="O379" t="n">
-        <v>464</v>
+        <v>678</v>
       </c>
       <c r="Q379" t="n">
         <v>0</v>
       </c>
       <c r="R379" t="n">
-        <v>0.2180324027633633</v>
+        <v>0.3185904505895697</v>
       </c>
       <c r="S379" t="inlineStr">
         <is>
@@ -69192,25 +69483,25 @@
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="N380" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O380" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q380" t="n">
         <v>0</v>
       </c>
       <c r="R380" t="n">
-        <v>0.01297982463651191</v>
+        <v>0.004326608212170636</v>
       </c>
       <c r="S380" t="inlineStr">
         <is>
@@ -69277,6 +69568,894 @@
         </is>
       </c>
       <c r="BC380" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="N381" t="n">
+        <v>695</v>
+      </c>
+      <c r="O381" t="n">
+        <v>695</v>
+      </c>
+      <c r="Q381" t="n">
+        <v>0</v>
+      </c>
+      <c r="R381" t="n">
+        <v>0.3265787067252964</v>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO381" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP381" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR381" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS381" t="inlineStr"/>
+      <c r="AT381" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU381" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV381" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW381" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX381" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY381" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA381" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB381" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC381" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="N382" t="n">
+        <v>3</v>
+      </c>
+      <c r="O382" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q382" t="n">
+        <v>0</v>
+      </c>
+      <c r="R382" t="n">
+        <v>0.01297982463651191</v>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO382" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP382" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR382" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS382" t="inlineStr"/>
+      <c r="AT382" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU382" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV382" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW382" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX382" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY382" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ382" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA382" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB382" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC382" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="N383" t="n">
+        <v>565</v>
+      </c>
+      <c r="O383" t="n">
+        <v>565</v>
+      </c>
+      <c r="Q383" t="n">
+        <v>0</v>
+      </c>
+      <c r="R383" t="n">
+        <v>0.2654920421579747</v>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO383" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP383" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR383" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS383" t="inlineStr"/>
+      <c r="AT383" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU383" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV383" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW383" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX383" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY383" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ383" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA383" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB383" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC383" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="N384" t="n">
+        <v>2</v>
+      </c>
+      <c r="O384" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q384" t="n">
+        <v>0</v>
+      </c>
+      <c r="R384" t="n">
+        <v>0.008653216424341272</v>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO384" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP384" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR384" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS384" t="inlineStr"/>
+      <c r="AT384" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU384" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV384" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW384" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX384" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY384" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA384" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB384" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC384" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="N385" t="n">
+        <v>464</v>
+      </c>
+      <c r="O385" t="n">
+        <v>464</v>
+      </c>
+      <c r="Q385" t="n">
+        <v>0</v>
+      </c>
+      <c r="R385" t="n">
+        <v>0.2180324027633633</v>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO385" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP385" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR385" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS385" t="inlineStr"/>
+      <c r="AT385" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU385" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV385" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW385" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX385" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY385" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA385" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB385" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC385" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="N386" t="n">
+        <v>3</v>
+      </c>
+      <c r="O386" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q386" t="n">
+        <v>0</v>
+      </c>
+      <c r="R386" t="n">
+        <v>0.01297982463651191</v>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO386" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP386" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR386" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS386" t="inlineStr"/>
+      <c r="AT386" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU386" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV386" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW386" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX386" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY386" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ386" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA386" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB386" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC386" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -69398,7 +70577,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -69408,7 +70587,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11">
@@ -69428,7 +70607,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -69460,7 +70639,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33729</v>
+        <v>33731</v>
       </c>
     </row>
     <row r="16">
